--- a/data/Zeres_MID_Register.xlsx
+++ b/data/Zeres_MID_Register.xlsx
@@ -13,6 +13,7 @@
     <sheet name="Conflicts" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Manifest" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Change Log" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Conformity" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +443,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
@@ -478,7 +478,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
@@ -535,7 +534,6 @@
         </is>
       </c>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
@@ -599,7 +597,6 @@
         </is>
       </c>
     </row>
-    <row r="28"/>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
@@ -642,7 +639,6 @@
         </is>
       </c>
     </row>
-    <row r="35"/>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
@@ -49059,4 +49055,100 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="50" customWidth="1" min="12" max="12"/>
+    <col width="80" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Certificate Number</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Issuing Body</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Directive Cited</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Models Covered</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Document Link</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Drive File</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>SHA-256</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Date Added</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Added By</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Review Needed</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/Zeres_MID_Register.xlsx
+++ b/data/Zeres_MID_Register.xlsx
@@ -846,7 +846,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S381"/>
+  <dimension ref="A1:S448"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -27186,6 +27186,4405 @@
         </is>
       </c>
       <c r="S381" t="inlineStr"/>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>chg_0381</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>AlphaESS</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>SMILE G3 ECVT</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr"/>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr"/>
+      <c r="H382" t="inlineStr"/>
+      <c r="I382" t="inlineStr">
+        <is>
+          <t>https://alphaess.solshare.nl/producten/smile-g3-laadpaal</t>
+        </is>
+      </c>
+      <c r="J382" t="inlineStr"/>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>Technical/Chargers/AC Chargers/AlphaESS</t>
+        </is>
+      </c>
+      <c r="L382" t="inlineStr">
+        <is>
+          <t>Needs Research</t>
+        </is>
+      </c>
+      <c r="M382" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="N382" t="inlineStr"/>
+      <c r="O382" t="inlineStr"/>
+      <c r="P382" t="inlineStr"/>
+      <c r="Q382" t="inlineStr">
+        <is>
+          <t>Added 2026-08-20 from Zeres laadpalen list v19 Aug 2026; not manufacturer-verified and not previously in the register. Confirm against a primary source before quoting a client.</t>
+        </is>
+      </c>
+      <c r="R382" t="inlineStr">
+        <is>
+          <t>Geen MID meter
+[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Nee'; recorded as None because list says 'Nee' and the note does not qualify it.</t>
+        </is>
+      </c>
+      <c r="S382" t="inlineStr"/>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>chg_0382</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>Autel</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>Ultra</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr"/>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr"/>
+      <c r="H383" t="inlineStr"/>
+      <c r="I383" t="inlineStr">
+        <is>
+          <t>https://autelenergy.eu/en-EU</t>
+        </is>
+      </c>
+      <c r="J383" t="inlineStr"/>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>Technical/Chargers/AC Chargers/Autel</t>
+        </is>
+      </c>
+      <c r="L383" t="inlineStr">
+        <is>
+          <t>Needs Research</t>
+        </is>
+      </c>
+      <c r="M383" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="N383" t="inlineStr"/>
+      <c r="O383" t="inlineStr"/>
+      <c r="P383" t="inlineStr"/>
+      <c r="Q383" t="inlineStr">
+        <is>
+          <t>Added 2026-08-20 from Zeres laadpalen list v19 Aug 2026; not manufacturer-verified and not previously in the register. Confirm against a primary source before quoting a client.</t>
+        </is>
+      </c>
+      <c r="R383" t="inlineStr">
+        <is>
+          <t>Autel Ultra DC-snellader is primair voor de Noord-Amerikaanse markt en heeft geen Europese MID-certificering.
+[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Nee'; recorded as Unknown because the note says this is not on the EU market ('Noord-Amerikaanse markt'); a charger that cannot be bought here cannot be booked into the REV, whatever its metering.</t>
+        </is>
+      </c>
+      <c r="S383" t="inlineStr"/>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>chg_0383</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>Autel</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>Wallbox AC MaxiCharger</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr"/>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>Integrated</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr"/>
+      <c r="H384" t="inlineStr"/>
+      <c r="I384" t="inlineStr">
+        <is>
+          <t>https://autelenergy.com/en-EU/media-bank/product-center?product=ac-wallbox</t>
+        </is>
+      </c>
+      <c r="J384" t="inlineStr"/>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>Technical/Chargers/AC Chargers/Autel</t>
+        </is>
+      </c>
+      <c r="L384" t="inlineStr">
+        <is>
+          <t>Needs Research</t>
+        </is>
+      </c>
+      <c r="M384" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="N384" t="inlineStr"/>
+      <c r="O384" t="inlineStr"/>
+      <c r="P384" t="inlineStr"/>
+      <c r="Q384" t="inlineStr">
+        <is>
+          <t>Added 2026-08-20 from Zeres laadpalen list v19 Aug 2026; not manufacturer-verified and not previously in the register. Confirm against a primary source before quoting a client.</t>
+        </is>
+      </c>
+      <c r="R384" t="inlineStr">
+        <is>
+          <t>JA, mits lCD scherm
+[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Ja'; recorded as Integrated because list says 'Ja' and the note does not qualify it.</t>
+        </is>
+      </c>
+      <c r="S384" t="inlineStr"/>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>chg_0384</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>Autel</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>Pro</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr"/>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr"/>
+      <c r="H385" t="inlineStr"/>
+      <c r="I385" t="inlineStr">
+        <is>
+          <t>https://autelenergy.eu/en-EU</t>
+        </is>
+      </c>
+      <c r="J385" t="inlineStr"/>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>Technical/Chargers/AC Chargers/Autel</t>
+        </is>
+      </c>
+      <c r="L385" t="inlineStr">
+        <is>
+          <t>Needs Research</t>
+        </is>
+      </c>
+      <c r="M385" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="N385" t="inlineStr"/>
+      <c r="O385" t="inlineStr"/>
+      <c r="P385" t="inlineStr"/>
+      <c r="Q385" t="inlineStr">
+        <is>
+          <t>Added 2026-08-20 from Zeres laadpalen list v19 Aug 2026; not manufacturer-verified and not previously in the register. Confirm against a primary source before quoting a client.</t>
+        </is>
+      </c>
+      <c r="R385" t="inlineStr">
+        <is>
+          <t>Autel Pro DC-snellader is primair voor de Noord-Amerikaanse markt en heeft geen Europese MID-certificering.
+[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Nee'; recorded as Unknown because the note says this is not on the EU market ('Noord-Amerikaanse markt'); a charger that cannot be bought here cannot be booked into the REV, whatever its metering.</t>
+        </is>
+      </c>
+      <c r="S385" t="inlineStr"/>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>chg_0385</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>Besen</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>BS20 (alle varianten)</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr"/>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr"/>
+      <c r="H386" t="inlineStr"/>
+      <c r="I386" t="inlineStr">
+        <is>
+          <t>https://www.wallboxdiscounter.com/en/besen-11-kw-type-2-socket-ev-charger.html</t>
+        </is>
+      </c>
+      <c r="J386" t="inlineStr"/>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>Technical/Chargers/AC Chargers/Besen</t>
+        </is>
+      </c>
+      <c r="L386" t="inlineStr">
+        <is>
+          <t>Needs Research</t>
+        </is>
+      </c>
+      <c r="M386" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="N386" t="inlineStr"/>
+      <c r="O386" t="inlineStr"/>
+      <c r="P386" t="inlineStr"/>
+      <c r="Q386" t="inlineStr">
+        <is>
+          <t>Added 2026-08-20 from Zeres laadpalen list v19 Aug 2026; not manufacturer-verified and not previously in the register. Confirm against a primary source before quoting a client.</t>
+        </is>
+      </c>
+      <c r="R386" t="inlineStr">
+        <is>
+          <t>Besen BS20-serie (7.4kW, 11kW, 22kW) heeft geen MID-meter in geen enkele variant. Bevestigd via wallboxdiscounter.com productpagina ('MID Meter: No') voor BS20-BC-11KW-RFID, BS20-BC-22KW-APP en BS20-BA-11KW-APP.
+[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Nee'; recorded as None because list says 'Nee' and the note does not qualify it.</t>
+        </is>
+      </c>
+      <c r="S386" t="inlineStr"/>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>chg_0386</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>BlueBuilt (Coolblue)</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>Prodrive (met M23/M24 op de laadpaal)</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr"/>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>Integrated</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr"/>
+      <c r="H387" t="inlineStr"/>
+      <c r="I387" t="inlineStr">
+        <is>
+          <t>M23 of M24 op laadpaal zichtbaar</t>
+        </is>
+      </c>
+      <c r="J387" t="inlineStr"/>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>Technical/Chargers/AC Chargers/BlueBuilt (Coolblue)</t>
+        </is>
+      </c>
+      <c r="L387" t="inlineStr">
+        <is>
+          <t>Needs Research</t>
+        </is>
+      </c>
+      <c r="M387" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="N387" t="inlineStr"/>
+      <c r="O387" t="inlineStr"/>
+      <c r="P387" t="inlineStr"/>
+      <c r="Q387" t="inlineStr">
+        <is>
+          <t>Added 2026-08-20 from Zeres laadpalen list v19 Aug 2026; not manufacturer-verified and not previously in the register. Confirm against a primary source before quoting a client.</t>
+        </is>
+      </c>
+      <c r="R387" t="inlineStr">
+        <is>
+          <t>Aanvankelijk heeft Coolblue laders zonder MID meter geleverd met deze naam. Met Prodrive zijn de laadpalen wel voorzien van een MID meter
+[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Ja'; recorded as Integrated because list says 'Ja' and the note does not qualify it.</t>
+        </is>
+      </c>
+      <c r="S387" t="inlineStr"/>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>chg_0387</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>Blue Current</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>Hidden</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr"/>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>Integrated</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr"/>
+      <c r="H388" t="inlineStr"/>
+      <c r="I388" t="inlineStr">
+        <is>
+          <t>Datasheet ontvangen van Blue Current</t>
+        </is>
+      </c>
+      <c r="J388" t="inlineStr"/>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>Technical/Chargers/AC Chargers/Blue Current</t>
+        </is>
+      </c>
+      <c r="L388" t="inlineStr">
+        <is>
+          <t>Needs Research</t>
+        </is>
+      </c>
+      <c r="M388" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="N388" t="inlineStr"/>
+      <c r="O388" t="inlineStr"/>
+      <c r="P388" t="inlineStr"/>
+      <c r="Q388" t="inlineStr">
+        <is>
+          <t>Added 2026-08-20 from Zeres laadpalen list v19 Aug 2026; not manufacturer-verified and not previously in the register. Confirm against a primary source before quoting a client.</t>
+        </is>
+      </c>
+      <c r="R388" t="inlineStr">
+        <is>
+          <t>Blue Current Hidden heeft een MID-meter . Bevestigd via Blue Current productsheet.
+[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Ja'; recorded as Integrated because list says 'Ja' and the note does not qualify it.</t>
+        </is>
+      </c>
+      <c r="S388" t="inlineStr"/>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>chg_0388</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>Bue Marble</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>Ostra Home of Home &amp; Work</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr"/>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="G389" t="inlineStr"/>
+      <c r="H389" t="inlineStr"/>
+      <c r="I389" t="inlineStr"/>
+      <c r="J389" t="inlineStr"/>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>Technical/Chargers/AC Chargers/Bue Marble</t>
+        </is>
+      </c>
+      <c r="L389" t="inlineStr">
+        <is>
+          <t>Needs Research</t>
+        </is>
+      </c>
+      <c r="M389" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="N389" t="inlineStr"/>
+      <c r="O389" t="inlineStr"/>
+      <c r="P389" t="inlineStr"/>
+      <c r="Q389" t="inlineStr">
+        <is>
+          <t>Added 2026-08-20 from Zeres laadpalen list v19 Aug 2026; not manufacturer-verified and not previously in the register. Confirm against a primary source before quoting a client.</t>
+        </is>
+      </c>
+      <c r="R389" t="inlineStr">
+        <is>
+          <t>De fabrikant heeft geen datasheet maar het lijkt erop dat er wel een MID meter in de laadpaal zit: dit wordt onderzocht
+[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Misschien'; recorded as Optional because list says 'Misschien' and the note does not qualify it.</t>
+        </is>
+      </c>
+      <c r="S389" t="inlineStr"/>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>chg_0389</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>Cfos</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>Brain Power wallbox 22kW Gen 1</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr"/>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>Integrated</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr"/>
+      <c r="H390" t="inlineStr"/>
+      <c r="I390" t="inlineStr">
+        <is>
+          <t>https://www.cfos-power.com/en-us/cfos-power-brain-wallbox/cfos-power-brain-wallbox.htm</t>
+        </is>
+      </c>
+      <c r="J390" t="inlineStr"/>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>Technical/Chargers/AC Chargers/Cfos</t>
+        </is>
+      </c>
+      <c r="L390" t="inlineStr">
+        <is>
+          <t>Needs Research</t>
+        </is>
+      </c>
+      <c r="M390" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="N390" t="inlineStr"/>
+      <c r="O390" t="inlineStr"/>
+      <c r="P390" t="inlineStr"/>
+      <c r="Q390" t="inlineStr">
+        <is>
+          <t>Added 2026-08-20 from Zeres laadpalen list v19 Aug 2026; not manufacturer-verified and not previously in the register. Confirm against a primary source before quoting a client.</t>
+        </is>
+      </c>
+      <c r="R390" t="inlineStr">
+        <is>
+          <t>Cfos Brain Power wallbox 22kW Gen 1 heeft een ingebouwde MID-gecertificeerde meter. Bevestigd via Cfos productinformatie.
+[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Ja'; recorded as Integrated because list says 'Ja' and the note does not qualify it.</t>
+        </is>
+      </c>
+      <c r="S390" t="inlineStr"/>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>chg_0390</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>CoolBlue</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>BlueBuilt 1 model</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr"/>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr"/>
+      <c r="H391" t="inlineStr"/>
+      <c r="I391" t="inlineStr">
+        <is>
+          <t>https://www.coolblue.nl/laadpalen</t>
+        </is>
+      </c>
+      <c r="J391" t="inlineStr"/>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>Technical/Chargers/AC Chargers/CoolBlue</t>
+        </is>
+      </c>
+      <c r="L391" t="inlineStr">
+        <is>
+          <t>Needs Research</t>
+        </is>
+      </c>
+      <c r="M391" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="N391" t="inlineStr"/>
+      <c r="O391" t="inlineStr"/>
+      <c r="P391" t="inlineStr"/>
+      <c r="Q391" t="inlineStr">
+        <is>
+          <t>Added 2026-08-20 from Zeres laadpalen list v19 Aug 2026; not manufacturer-verified and not previously in the register. Confirm against a primary source before quoting a client.</t>
+        </is>
+      </c>
+      <c r="R391" t="inlineStr">
+        <is>
+          <t>CoolBlue BlueBuilt laadpaal is een Peblar whitelabel. MID-meter is een optie, niet standaard ingebouwd. Bevestigd via Peblar/CoolBlue productinformatie.
+[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Misschien'; recorded as Optional because note describes an option or variant ('MID-meter is een optie').</t>
+        </is>
+      </c>
+      <c r="S391" t="inlineStr"/>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>chg_0391</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>Cube</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr"/>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr"/>
+      <c r="H392" t="inlineStr"/>
+      <c r="I392" t="inlineStr">
+        <is>
+          <t>https://www.zeres.nl</t>
+        </is>
+      </c>
+      <c r="J392" t="inlineStr"/>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>Technical/Chargers/AC Chargers/Cube</t>
+        </is>
+      </c>
+      <c r="L392" t="inlineStr">
+        <is>
+          <t>Needs Research</t>
+        </is>
+      </c>
+      <c r="M392" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="N392" t="inlineStr"/>
+      <c r="O392" t="inlineStr"/>
+      <c r="P392" t="inlineStr"/>
+      <c r="Q392" t="inlineStr">
+        <is>
+          <t>Added 2026-08-20 from Zeres laadpalen list v19 Aug 2026; not manufacturer-verified and not previously in the register. Confirm against a primary source before quoting a client.</t>
+        </is>
+      </c>
+      <c r="R392" t="inlineStr">
+        <is>
+          <t>Cube Basic laadpaal is verkrijgbaar met en zonder MID-meter als optie. Bron: Zeres verificatienota.
+[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Misschien'; recorded as Optional because list says 'Misschien' and the note does not qualify it.</t>
+        </is>
+      </c>
+      <c r="S392" t="inlineStr"/>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>chg_0392</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>Cube</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>Smart+</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr"/>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="G393" t="inlineStr"/>
+      <c r="H393" t="inlineStr"/>
+      <c r="I393" t="inlineStr">
+        <is>
+          <t>https://www.zeres.nl</t>
+        </is>
+      </c>
+      <c r="J393" t="inlineStr"/>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>Technical/Chargers/AC Chargers/Cube</t>
+        </is>
+      </c>
+      <c r="L393" t="inlineStr">
+        <is>
+          <t>Needs Research</t>
+        </is>
+      </c>
+      <c r="M393" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="N393" t="inlineStr"/>
+      <c r="O393" t="inlineStr"/>
+      <c r="P393" t="inlineStr"/>
+      <c r="Q393" t="inlineStr">
+        <is>
+          <t>Added 2026-08-20 from Zeres laadpalen list v19 Aug 2026; not manufacturer-verified and not previously in the register. Confirm against a primary source before quoting a client.</t>
+        </is>
+      </c>
+      <c r="R393" t="inlineStr">
+        <is>
+          <t>Cube Smart+ laadpaal is verkrijgbaar met en zonder MID-meter als optie. Bron: Zeres verificatienota.
+[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Misschien'; recorded as Optional because list says 'Misschien' and the note does not qualify it.</t>
+        </is>
+      </c>
+      <c r="S393" t="inlineStr"/>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>chg_0393</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>DIC</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>Charge Easy</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr"/>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>Integrated</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr"/>
+      <c r="H394" t="inlineStr"/>
+      <c r="I394" t="inlineStr">
+        <is>
+          <t>Bevestigd door fabrikant: document beschikbaar bij Zeres</t>
+        </is>
+      </c>
+      <c r="J394" t="inlineStr"/>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>Technical/Chargers/AC Chargers/DIC</t>
+        </is>
+      </c>
+      <c r="L394" t="inlineStr">
+        <is>
+          <t>Needs Research</t>
+        </is>
+      </c>
+      <c r="M394" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="N394" t="inlineStr"/>
+      <c r="O394" t="inlineStr"/>
+      <c r="P394" t="inlineStr"/>
+      <c r="Q394" t="inlineStr">
+        <is>
+          <t>Added 2026-08-20 from Zeres laadpalen list v19 Aug 2026; not manufacturer-verified and not previously in the register. Confirm against a primary source before quoting a client.</t>
+        </is>
+      </c>
+      <c r="R394" t="inlineStr">
+        <is>
+          <t>DIC Charge Easy, model 50122 heeft een MID meter
+[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Ja'; recorded as Integrated because list says 'Ja' and the note does not qualify it.</t>
+        </is>
+      </c>
+      <c r="S394" t="inlineStr"/>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>chg_0394</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>DIC</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>Laadzuil</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr"/>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>Integrated</t>
+        </is>
+      </c>
+      <c r="G395" t="inlineStr"/>
+      <c r="H395" t="inlineStr"/>
+      <c r="I395" t="inlineStr">
+        <is>
+          <t>Bevestigd door fabrikant: document beschikbaar bij Zeres</t>
+        </is>
+      </c>
+      <c r="J395" t="inlineStr"/>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>Technical/Chargers/AC Chargers/DIC</t>
+        </is>
+      </c>
+      <c r="L395" t="inlineStr">
+        <is>
+          <t>Needs Research</t>
+        </is>
+      </c>
+      <c r="M395" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="N395" t="inlineStr"/>
+      <c r="O395" t="inlineStr"/>
+      <c r="P395" t="inlineStr"/>
+      <c r="Q395" t="inlineStr">
+        <is>
+          <t>Added 2026-08-20 from Zeres laadpalen list v19 Aug 2026; not manufacturer-verified and not previously in the register. Confirm against a primary source before quoting a client.</t>
+        </is>
+      </c>
+      <c r="R395" t="inlineStr">
+        <is>
+          <t>DIC Laadzuil: heeft wel MID meter.
+[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Ja'; recorded as Integrated because list says 'Ja' and the note does not qualify it.</t>
+        </is>
+      </c>
+      <c r="S395" t="inlineStr"/>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>chg_0395</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>Easee</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>Up</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr"/>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G396" t="inlineStr"/>
+      <c r="H396" t="inlineStr"/>
+      <c r="I396" t="inlineStr">
+        <is>
+          <t>https://easee.com/nl-nl/products/</t>
+        </is>
+      </c>
+      <c r="J396" t="inlineStr"/>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>Technical/Chargers/AC Chargers/Easee</t>
+        </is>
+      </c>
+      <c r="L396" t="inlineStr">
+        <is>
+          <t>Needs Research</t>
+        </is>
+      </c>
+      <c r="M396" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="N396" t="inlineStr"/>
+      <c r="O396" t="inlineStr"/>
+      <c r="P396" t="inlineStr"/>
+      <c r="Q396" t="inlineStr">
+        <is>
+          <t>Added 2026-08-20 from Zeres laadpalen list v19 Aug 2026; not manufacturer-verified and not previously in the register. Confirm against a primary source before quoting a client.</t>
+        </is>
+      </c>
+      <c r="R396" t="inlineStr">
+        <is>
+          <t>Easee Charge Up heeft geen ingebouwde MID-meter. Bevestigd via Easee productinformatie.
+[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Nee'; recorded as None because list says 'Nee' and the note does not qualify it.</t>
+        </is>
+      </c>
+      <c r="S396" t="inlineStr"/>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>chg_0396</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>Easee</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr"/>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>Integrated</t>
+        </is>
+      </c>
+      <c r="G397" t="inlineStr"/>
+      <c r="H397" t="inlineStr"/>
+      <c r="I397" t="inlineStr">
+        <is>
+          <t>https://easee.com/nl-nl/products/charge-max/</t>
+        </is>
+      </c>
+      <c r="J397" t="inlineStr"/>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>Technical/Chargers/AC Chargers/Easee</t>
+        </is>
+      </c>
+      <c r="L397" t="inlineStr">
+        <is>
+          <t>Needs Research</t>
+        </is>
+      </c>
+      <c r="M397" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="N397" t="inlineStr"/>
+      <c r="O397" t="inlineStr"/>
+      <c r="P397" t="inlineStr"/>
+      <c r="Q397" t="inlineStr">
+        <is>
+          <t>Added 2026-08-20 from Zeres laadpalen list v19 Aug 2026; not manufacturer-verified and not previously in the register. Confirm against a primary source before quoting a client.</t>
+        </is>
+      </c>
+      <c r="R397" t="inlineStr">
+        <is>
+          <t>Easee Charge Max heeft een ingebouwde MID-gecertificeerde meter (klasse B). Bevestigd via Easee Charge Max productpagina en datasheet.
+[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Ja'; recorded as Integrated because list says 'Ja' and the note does not qualify it.</t>
+        </is>
+      </c>
+      <c r="S397" t="inlineStr"/>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>chg_0397</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>Easee</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr"/>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G398" t="inlineStr"/>
+      <c r="H398" t="inlineStr"/>
+      <c r="I398" t="inlineStr">
+        <is>
+          <t>https://easee.com/nl-nl/products/</t>
+        </is>
+      </c>
+      <c r="J398" t="inlineStr"/>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>Technical/Chargers/AC Chargers/Easee</t>
+        </is>
+      </c>
+      <c r="L398" t="inlineStr">
+        <is>
+          <t>Needs Research</t>
+        </is>
+      </c>
+      <c r="M398" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="N398" t="inlineStr"/>
+      <c r="O398" t="inlineStr"/>
+      <c r="P398" t="inlineStr"/>
+      <c r="Q398" t="inlineStr">
+        <is>
+          <t>Added 2026-08-20 from Zeres laadpalen list v19 Aug 2026; not manufacturer-verified and not previously in the register. Confirm against a primary source before quoting a client.</t>
+        </is>
+      </c>
+      <c r="R398" t="inlineStr">
+        <is>
+          <t>Easee Core heeft geen ingebouwde MID-meter. Bevestigd via Easee productinformatie.
+[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Nee'; recorded as None because list says 'Nee' and the note does not qualify it.</t>
+        </is>
+      </c>
+      <c r="S398" t="inlineStr"/>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>chg_0398</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>Ecotap</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>Duo Wide XL</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr"/>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>Integrated</t>
+        </is>
+      </c>
+      <c r="G399" t="inlineStr"/>
+      <c r="H399" t="inlineStr"/>
+      <c r="I399" t="inlineStr">
+        <is>
+          <t>https://ecotap.nl/wp-content/uploads/2025/06/Duo-Wide-XL-specs-EN.pdf</t>
+        </is>
+      </c>
+      <c r="J399" t="inlineStr"/>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>Technical/Chargers/AC Chargers/Ecotap</t>
+        </is>
+      </c>
+      <c r="L399" t="inlineStr">
+        <is>
+          <t>Needs Research</t>
+        </is>
+      </c>
+      <c r="M399" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="N399" t="inlineStr"/>
+      <c r="O399" t="inlineStr"/>
+      <c r="P399" t="inlineStr"/>
+      <c r="Q399" t="inlineStr">
+        <is>
+          <t>Added 2026-08-20 from Zeres laadpalen list v19 Aug 2026; not manufacturer-verified and not previously in the register. Confirm against a primary source before quoting a client.</t>
+        </is>
+      </c>
+      <c r="R399" t="inlineStr">
+        <is>
+          <t>Ecotap Duo Wide XL heeft een ingebouwde MID-gecertificeerde meter. Bevestigd via Ecotap website.
+[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Ja'; recorded as Integrated because list says 'Ja' and the note does not qualify it.</t>
+        </is>
+      </c>
+      <c r="S399" t="inlineStr"/>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>chg_0399</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>Ecotap</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>Duo Wide Plus</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr"/>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>Integrated</t>
+        </is>
+      </c>
+      <c r="G400" t="inlineStr"/>
+      <c r="H400" t="inlineStr"/>
+      <c r="I400" t="inlineStr">
+        <is>
+          <t>https://ecotap.nl/wp-content/uploads/2025/06/Duo-Wide-Plus-specs-EN.pdf</t>
+        </is>
+      </c>
+      <c r="J400" t="inlineStr"/>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>Technical/Chargers/AC Chargers/Ecotap</t>
+        </is>
+      </c>
+      <c r="L400" t="inlineStr">
+        <is>
+          <t>Needs Research</t>
+        </is>
+      </c>
+      <c r="M400" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="N400" t="inlineStr"/>
+      <c r="O400" t="inlineStr"/>
+      <c r="P400" t="inlineStr"/>
+      <c r="Q400" t="inlineStr">
+        <is>
+          <t>Added 2026-08-20 from Zeres laadpalen list v19 Aug 2026; not manufacturer-verified and not previously in the register. Confirm against a primary source before quoting a client.</t>
+        </is>
+      </c>
+      <c r="R400" t="inlineStr">
+        <is>
+          <t>Ecotap Duo Wide Plus heeft een ingebouwde MID-gecertificeerde meter. Bevestigd via Ecotap website.
+[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Ja'; recorded as Integrated because list says 'Ja' and the note does not qualify it.</t>
+        </is>
+      </c>
+      <c r="S400" t="inlineStr"/>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>chg_0400</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>Elli</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>Connect 2</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr"/>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G401" t="inlineStr"/>
+      <c r="H401" t="inlineStr"/>
+      <c r="I401" t="inlineStr">
+        <is>
+          <t>Datasheet in verzameling Zeres</t>
+        </is>
+      </c>
+      <c r="J401" t="inlineStr"/>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>Technical/Chargers/AC Chargers/Elli</t>
+        </is>
+      </c>
+      <c r="L401" t="inlineStr">
+        <is>
+          <t>Needs Research</t>
+        </is>
+      </c>
+      <c r="M401" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="N401" t="inlineStr"/>
+      <c r="O401" t="inlineStr"/>
+      <c r="P401" t="inlineStr"/>
+      <c r="Q401" t="inlineStr">
+        <is>
+          <t>Added 2026-08-20 from Zeres laadpalen list v19 Aug 2026; not manufacturer-verified and not previously in the register. Confirm against a primary source before quoting a client.</t>
+        </is>
+      </c>
+      <c r="R401" t="inlineStr">
+        <is>
+          <t>Voor Volkswagen, SKoda, Seat: geen MID meter.
+[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Nee'; recorded as None because list says 'Nee' and the note does not qualify it.</t>
+        </is>
+      </c>
+      <c r="S401" t="inlineStr"/>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>chg_0401</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>Elli</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>Charger Pro (2)</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr"/>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>Integrated</t>
+        </is>
+      </c>
+      <c r="G402" t="inlineStr"/>
+      <c r="H402" t="inlineStr"/>
+      <c r="I402" t="inlineStr">
+        <is>
+          <t>Datasheet in verzameling Zeres</t>
+        </is>
+      </c>
+      <c r="J402" t="inlineStr"/>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>Technical/Chargers/AC Chargers/Elli</t>
+        </is>
+      </c>
+      <c r="L402" t="inlineStr">
+        <is>
+          <t>Needs Research</t>
+        </is>
+      </c>
+      <c r="M402" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="N402" t="inlineStr"/>
+      <c r="O402" t="inlineStr"/>
+      <c r="P402" t="inlineStr"/>
+      <c r="Q402" t="inlineStr">
+        <is>
+          <t>Added 2026-08-20 from Zeres laadpalen list v19 Aug 2026; not manufacturer-verified and not previously in the register. Confirm against a primary source before quoting a client.</t>
+        </is>
+      </c>
+      <c r="R402" t="inlineStr">
+        <is>
+          <t>Voor Volkswagen, SKoda, Seat: wel MID meter.
+[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Ja'; recorded as Integrated because list says 'Ja' and the note does not qualify it.</t>
+        </is>
+      </c>
+      <c r="S402" t="inlineStr"/>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>chg_0402</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>Eneco Mobility</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>Connectric</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr"/>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>Integrated</t>
+        </is>
+      </c>
+      <c r="G403" t="inlineStr"/>
+      <c r="H403" t="inlineStr"/>
+      <c r="I403" t="inlineStr">
+        <is>
+          <t>https://www.eneco-emobility.com/thuis/laadpaal/aanvragen/ 
+Zeres heeft het aan Eneco gevraagd en per email bevestiging gekregen.</t>
+        </is>
+      </c>
+      <c r="J403" t="inlineStr"/>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>Technical/Chargers/AC Chargers/Eneco Mobility</t>
+        </is>
+      </c>
+      <c r="L403" t="inlineStr">
+        <is>
+          <t>Needs Research</t>
+        </is>
+      </c>
+      <c r="M403" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="N403" t="inlineStr"/>
+      <c r="O403" t="inlineStr"/>
+      <c r="P403" t="inlineStr"/>
+      <c r="Q403" t="inlineStr">
+        <is>
+          <t>Added 2026-08-20 from Zeres laadpalen list v19 Aug 2026; not manufacturer-verified and not previously in the register. Confirm against a primary source before quoting a client.</t>
+        </is>
+      </c>
+      <c r="R403" t="inlineStr">
+        <is>
+          <t>Eneco Mobility bevestigt dat de Connectric voldoet aan MID zonder een datasheet te verstrekken
+[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Ja'; recorded as Integrated because list says 'Ja' and the note does not qualify it.</t>
+        </is>
+      </c>
+      <c r="S403" t="inlineStr"/>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>chg_0403</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>Flexicharge</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr"/>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>Integrated</t>
+        </is>
+      </c>
+      <c r="G404" t="inlineStr"/>
+      <c r="H404" t="inlineStr"/>
+      <c r="I404" t="inlineStr">
+        <is>
+          <t>opgave via website fabrikant</t>
+        </is>
+      </c>
+      <c r="J404" t="inlineStr"/>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>Technical/Chargers/AC Chargers/Flexicharge</t>
+        </is>
+      </c>
+      <c r="L404" t="inlineStr">
+        <is>
+          <t>Needs Research</t>
+        </is>
+      </c>
+      <c r="M404" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="N404" t="inlineStr"/>
+      <c r="O404" t="inlineStr"/>
+      <c r="P404" t="inlineStr"/>
+      <c r="Q404" t="inlineStr">
+        <is>
+          <t>Added 2026-08-20 from Zeres laadpalen list v19 Aug 2026; not manufacturer-verified and not previously in the register. Confirm against a primary source before quoting a client.</t>
+        </is>
+      </c>
+      <c r="R404" t="inlineStr">
+        <is>
+          <t>Al onze laadpalen worden standaard geleverd met een geïntegreerde MID‑gecertificeerde kWh‑meter
+[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Ja'; recorded as Integrated because list says 'Ja' and the note does not qualify it.</t>
+        </is>
+      </c>
+      <c r="S404" t="inlineStr"/>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>chg_0404</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>Flexicharge</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>Business Duo/Business Solo</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr"/>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>Integrated</t>
+        </is>
+      </c>
+      <c r="G405" t="inlineStr"/>
+      <c r="H405" t="inlineStr"/>
+      <c r="I405" t="inlineStr">
+        <is>
+          <t>opgave via website fabrikant</t>
+        </is>
+      </c>
+      <c r="J405" t="inlineStr"/>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>Technical/Chargers/AC Chargers/Flexicharge</t>
+        </is>
+      </c>
+      <c r="L405" t="inlineStr">
+        <is>
+          <t>Needs Research</t>
+        </is>
+      </c>
+      <c r="M405" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="N405" t="inlineStr"/>
+      <c r="O405" t="inlineStr"/>
+      <c r="P405" t="inlineStr"/>
+      <c r="Q405" t="inlineStr">
+        <is>
+          <t>Added 2026-08-20 from Zeres laadpalen list v19 Aug 2026; not manufacturer-verified and not previously in the register. Confirm against a primary source before quoting a client.</t>
+        </is>
+      </c>
+      <c r="R405" t="inlineStr">
+        <is>
+          <t>Al onze laadpalen worden standaard geleverd met een geïntegreerde MID‑gecertificeerde kWh‑meter
+[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Ja'; recorded as Integrated because list says 'Ja' and the note does not qualify it.</t>
+        </is>
+      </c>
+      <c r="S405" t="inlineStr"/>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>chg_0405</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>Flexicharge</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>Business Wall Duo/Business Wall Solo</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr"/>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>Integrated</t>
+        </is>
+      </c>
+      <c r="G406" t="inlineStr"/>
+      <c r="H406" t="inlineStr"/>
+      <c r="I406" t="inlineStr">
+        <is>
+          <t>opgave via website fabrikant</t>
+        </is>
+      </c>
+      <c r="J406" t="inlineStr"/>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>Technical/Chargers/AC Chargers/Flexicharge</t>
+        </is>
+      </c>
+      <c r="L406" t="inlineStr">
+        <is>
+          <t>Needs Research</t>
+        </is>
+      </c>
+      <c r="M406" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="N406" t="inlineStr"/>
+      <c r="O406" t="inlineStr"/>
+      <c r="P406" t="inlineStr"/>
+      <c r="Q406" t="inlineStr">
+        <is>
+          <t>Added 2026-08-20 from Zeres laadpalen list v19 Aug 2026; not manufacturer-verified and not previously in the register. Confirm against a primary source before quoting a client.</t>
+        </is>
+      </c>
+      <c r="R406" t="inlineStr">
+        <is>
+          <t>Al onze laadpalen worden standaard geleverd met een geïntegreerde MID‑gecertificeerde kWh‑meter
+[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Ja'; recorded as Integrated because list says 'Ja' and the note does not qualify it.</t>
+        </is>
+      </c>
+      <c r="S406" t="inlineStr"/>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>chg_0406</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>Flexicharge</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>Business Transport</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr"/>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>Integrated</t>
+        </is>
+      </c>
+      <c r="G407" t="inlineStr"/>
+      <c r="H407" t="inlineStr"/>
+      <c r="I407" t="inlineStr">
+        <is>
+          <t>opgave via website fabrikant</t>
+        </is>
+      </c>
+      <c r="J407" t="inlineStr"/>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>Technical/Chargers/AC Chargers/Flexicharge</t>
+        </is>
+      </c>
+      <c r="L407" t="inlineStr">
+        <is>
+          <t>Needs Research</t>
+        </is>
+      </c>
+      <c r="M407" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="N407" t="inlineStr"/>
+      <c r="O407" t="inlineStr"/>
+      <c r="P407" t="inlineStr"/>
+      <c r="Q407" t="inlineStr">
+        <is>
+          <t>Added 2026-08-20 from Zeres laadpalen list v19 Aug 2026; not manufacturer-verified and not previously in the register. Confirm against a primary source before quoting a client.</t>
+        </is>
+      </c>
+      <c r="R407" t="inlineStr">
+        <is>
+          <t>Al onze laadpalen worden standaard geleverd met een geïntegreerde MID‑gecertificeerde kWh‑meter
+[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Ja'; recorded as Integrated because list says 'Ja' and the note does not qualify it.</t>
+        </is>
+      </c>
+      <c r="S407" t="inlineStr"/>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>chg_0407</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>Flexicharge</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr"/>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>Integrated</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr"/>
+      <c r="H408" t="inlineStr"/>
+      <c r="I408" t="inlineStr">
+        <is>
+          <t>opgave via website fabrikant</t>
+        </is>
+      </c>
+      <c r="J408" t="inlineStr"/>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>Technical/Chargers/AC Chargers/Flexicharge</t>
+        </is>
+      </c>
+      <c r="L408" t="inlineStr">
+        <is>
+          <t>Needs Research</t>
+        </is>
+      </c>
+      <c r="M408" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="N408" t="inlineStr"/>
+      <c r="O408" t="inlineStr"/>
+      <c r="P408" t="inlineStr"/>
+      <c r="Q408" t="inlineStr">
+        <is>
+          <t>Added 2026-08-20 from Zeres laadpalen list v19 Aug 2026; not manufacturer-verified and not previously in the register. Confirm against a primary source before quoting a client.</t>
+        </is>
+      </c>
+      <c r="R408" t="inlineStr">
+        <is>
+          <t>Al onze laadpalen worden standaard geleverd met een geïntegreerde MID‑gecertificeerde kWh‑meter
+[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Ja'; recorded as Integrated because list says 'Ja' and the note does not qualify it.</t>
+        </is>
+      </c>
+      <c r="S408" t="inlineStr"/>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>chg_0408</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>Garo</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>GLB (Entity, GLB, Wallbox)</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr"/>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G409" t="inlineStr"/>
+      <c r="H409" t="inlineStr"/>
+      <c r="I409" t="inlineStr">
+        <is>
+          <t>garo.se</t>
+        </is>
+      </c>
+      <c r="J409" t="inlineStr"/>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>Technical/Chargers/AC Chargers/Garo</t>
+        </is>
+      </c>
+      <c r="L409" t="inlineStr">
+        <is>
+          <t>Needs Research</t>
+        </is>
+      </c>
+      <c r="M409" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="N409" t="inlineStr"/>
+      <c r="O409" t="inlineStr"/>
+      <c r="P409" t="inlineStr"/>
+      <c r="Q409" t="inlineStr">
+        <is>
+          <t>Added 2026-08-20 from Zeres laadpalen list v19 Aug 2026; not manufacturer-verified and not previously in the register. Confirm against a primary source before quoting a client.</t>
+        </is>
+      </c>
+      <c r="R409" t="inlineStr">
+        <is>
+          <t>Diverse modellen, wel met meter maar geen MID meter.
+[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Nee'; recorded as None because list says 'Nee' and the note does not qualify it.</t>
+        </is>
+      </c>
+      <c r="S409" t="inlineStr"/>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>chg_0409</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>go-e</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>Flex of Core</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr"/>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G410" t="inlineStr"/>
+      <c r="H410" t="inlineStr"/>
+      <c r="I410" t="inlineStr">
+        <is>
+          <t>https://blueworldnederland.nl/wp-content/uploads/2025/02/go-e-gemini-flex-datasheet.pdf</t>
+        </is>
+      </c>
+      <c r="J410" t="inlineStr"/>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>Technical/Chargers/AC Chargers/go-e</t>
+        </is>
+      </c>
+      <c r="L410" t="inlineStr">
+        <is>
+          <t>Needs Research</t>
+        </is>
+      </c>
+      <c r="M410" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="N410" t="inlineStr"/>
+      <c r="O410" t="inlineStr"/>
+      <c r="P410" t="inlineStr"/>
+      <c r="Q410" t="inlineStr">
+        <is>
+          <t>Added 2026-08-20 from Zeres laadpalen list v19 Aug 2026; not manufacturer-verified and not previously in the register. Confirm against a primary source before quoting a client.</t>
+        </is>
+      </c>
+      <c r="R410" t="inlineStr">
+        <is>
+          <t>Geen MID meter
+[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Nee'; recorded as None because list says 'Nee' and the note does not qualify it.</t>
+        </is>
+      </c>
+      <c r="S410" t="inlineStr"/>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>chg_0410</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>go-e</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>Charger Pro</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr"/>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>Integrated</t>
+        </is>
+      </c>
+      <c r="G411" t="inlineStr"/>
+      <c r="H411" t="inlineStr"/>
+      <c r="I411" t="inlineStr">
+        <is>
+          <t>https://blueworldnederland.nl/laadoplossingen/go-e-laadstations/go-e-charger-pro/</t>
+        </is>
+      </c>
+      <c r="J411" t="inlineStr"/>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>Technical/Chargers/AC Chargers/go-e</t>
+        </is>
+      </c>
+      <c r="L411" t="inlineStr">
+        <is>
+          <t>Needs Research</t>
+        </is>
+      </c>
+      <c r="M411" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="N411" t="inlineStr"/>
+      <c r="O411" t="inlineStr"/>
+      <c r="P411" t="inlineStr"/>
+      <c r="Q411" t="inlineStr">
+        <is>
+          <t>Added 2026-08-20 from Zeres laadpalen list v19 Aug 2026; not manufacturer-verified and not previously in the register. Confirm against a primary source before quoting a client.</t>
+        </is>
+      </c>
+      <c r="R411" t="inlineStr">
+        <is>
+          <t>Met MID meter. Model wordt ook aangeduid als Charger Pro MID
+[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Ja'; recorded as Integrated because list says 'Ja' and the note does not qualify it.</t>
+        </is>
+      </c>
+      <c r="S411" t="inlineStr"/>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>chg_0411</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>Hey One</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>Connect Plus en de One Smart</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr"/>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>Integrated</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr"/>
+      <c r="H412" t="inlineStr"/>
+      <c r="I412" t="inlineStr">
+        <is>
+          <t>Bevestigd per email met productsheets door fabrikant.</t>
+        </is>
+      </c>
+      <c r="J412" t="inlineStr"/>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>Technical/Chargers/AC Chargers/Hey One</t>
+        </is>
+      </c>
+      <c r="L412" t="inlineStr">
+        <is>
+          <t>Needs Research</t>
+        </is>
+      </c>
+      <c r="M412" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="N412" t="inlineStr"/>
+      <c r="O412" t="inlineStr"/>
+      <c r="P412" t="inlineStr"/>
+      <c r="Q412" t="inlineStr">
+        <is>
+          <t>Added 2026-08-20 from Zeres laadpalen list v19 Aug 2026; not manufacturer-verified and not previously in the register. Confirm against a primary source before quoting a client.</t>
+        </is>
+      </c>
+      <c r="R412" t="inlineStr">
+        <is>
+          <t>Geschikt voor ERE: hebben een MID meter.
+[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Ja'; recorded as Integrated because list says 'Ja' and the note does not qualify it.</t>
+        </is>
+      </c>
+      <c r="S412" t="inlineStr"/>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>chg_0412</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>Inepro</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>Pro380 MID</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr"/>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>Integrated</t>
+        </is>
+      </c>
+      <c r="G413" t="inlineStr"/>
+      <c r="H413" t="inlineStr"/>
+      <c r="I413" t="inlineStr">
+        <is>
+          <t>https://www.inepro.com/en/products/energy-meters/pro380/</t>
+        </is>
+      </c>
+      <c r="J413" t="inlineStr"/>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>Technical/Chargers/AC Chargers/Inepro</t>
+        </is>
+      </c>
+      <c r="L413" t="inlineStr">
+        <is>
+          <t>Needs Research</t>
+        </is>
+      </c>
+      <c r="M413" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="N413" t="inlineStr"/>
+      <c r="O413" t="inlineStr"/>
+      <c r="P413" t="inlineStr"/>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>Added 2026-08-20 from Zeres laadpalen list v19 Aug 2026; not manufacturer-verified and not previously in the register. Confirm against a primary source before quoting a client.</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr">
+        <is>
+          <t>Inepro Pro380 MID is een MID-gecertificeerde energiemeter (geen laadpaal). Bevestigd via Inepro productinformatie.
+[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Ja'; recorded as Integrated because list says 'Ja' and the note does not qualify it.</t>
+        </is>
+      </c>
+      <c r="S413" t="inlineStr"/>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>chg_0413</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>KEBA</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>P30 A-series</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr"/>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G414" t="inlineStr"/>
+      <c r="H414" t="inlineStr"/>
+      <c r="I414" t="inlineStr">
+        <is>
+          <t>https://www.keba.com/en/emobility/products/charging-stations</t>
+        </is>
+      </c>
+      <c r="J414" t="inlineStr"/>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>Technical/Chargers/AC Chargers/KEBA</t>
+        </is>
+      </c>
+      <c r="L414" t="inlineStr">
+        <is>
+          <t>Needs Research</t>
+        </is>
+      </c>
+      <c r="M414" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="N414" t="inlineStr"/>
+      <c r="O414" t="inlineStr"/>
+      <c r="P414" t="inlineStr"/>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>Added 2026-08-20 from Zeres laadpalen list v19 Aug 2026; not manufacturer-verified and not previously in the register. Confirm against a primary source before quoting a client.</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr">
+        <is>
+          <t>KEBA P30 A-series heeft geen ingebouwde MID-meter. Bevestigd via KEBA productinformatie.
+[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Nee'; recorded as None because list says 'Nee' and the note does not qualify it.</t>
+        </is>
+      </c>
+      <c r="S414" t="inlineStr"/>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>chg_0414</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>KEBA</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>P30 C-series</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr"/>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="G415" t="inlineStr"/>
+      <c r="H415" t="inlineStr"/>
+      <c r="I415" t="inlineStr">
+        <is>
+          <t>https://www.keba.com/en/emobility/products/charging-stations</t>
+        </is>
+      </c>
+      <c r="J415" t="inlineStr"/>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>Technical/Chargers/AC Chargers/KEBA</t>
+        </is>
+      </c>
+      <c r="L415" t="inlineStr">
+        <is>
+          <t>Needs Research</t>
+        </is>
+      </c>
+      <c r="M415" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="N415" t="inlineStr"/>
+      <c r="O415" t="inlineStr"/>
+      <c r="P415" t="inlineStr"/>
+      <c r="Q415" t="inlineStr">
+        <is>
+          <t>Added 2026-08-20 from Zeres laadpalen list v19 Aug 2026; not manufacturer-verified and not previously in the register. Confirm against a primary source before quoting a client.</t>
+        </is>
+      </c>
+      <c r="R415" t="inlineStr">
+        <is>
+          <t>KEBA P30 C-series heeft MID als optie. Bevestigd via KEBA productinformatie.
+[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Misschien'; recorded as Optional because note describes an option or variant ('als optie').</t>
+        </is>
+      </c>
+      <c r="S415" t="inlineStr"/>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>chg_0415</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>KEBA</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>P30 X-series</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr"/>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="G416" t="inlineStr"/>
+      <c r="H416" t="inlineStr"/>
+      <c r="I416" t="inlineStr">
+        <is>
+          <t>https://www.keba.com/en/emobility/products/charging-stations</t>
+        </is>
+      </c>
+      <c r="J416" t="inlineStr"/>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>Technical/Chargers/AC Chargers/KEBA</t>
+        </is>
+      </c>
+      <c r="L416" t="inlineStr">
+        <is>
+          <t>Needs Research</t>
+        </is>
+      </c>
+      <c r="M416" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="N416" t="inlineStr"/>
+      <c r="O416" t="inlineStr"/>
+      <c r="P416" t="inlineStr"/>
+      <c r="Q416" t="inlineStr">
+        <is>
+          <t>Added 2026-08-20 from Zeres laadpalen list v19 Aug 2026; not manufacturer-verified and not previously in the register. Confirm against a primary source before quoting a client.</t>
+        </is>
+      </c>
+      <c r="R416" t="inlineStr">
+        <is>
+          <t>KEBA P30 X-series heeft MID als optie. Bevestigd via KEBA productinformatie.
+[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Misschien'; recorded as Optional because note describes an option or variant ('als optie').</t>
+        </is>
+      </c>
+      <c r="S416" t="inlineStr"/>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>chg_0416</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>Loxone</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>Wallbox 11kW 16A Tree (MID-variant)</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr"/>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="G417" t="inlineStr"/>
+      <c r="H417" t="inlineStr"/>
+      <c r="I417" t="inlineStr">
+        <is>
+          <t>https://www.loxone.com/nln/producten/wallbox/</t>
+        </is>
+      </c>
+      <c r="J417" t="inlineStr"/>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>Technical/Chargers/AC Chargers/Loxone</t>
+        </is>
+      </c>
+      <c r="L417" t="inlineStr">
+        <is>
+          <t>Needs Research</t>
+        </is>
+      </c>
+      <c r="M417" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="N417" t="inlineStr"/>
+      <c r="O417" t="inlineStr"/>
+      <c r="P417" t="inlineStr"/>
+      <c r="Q417" t="inlineStr">
+        <is>
+          <t>Added 2026-08-20 from Zeres laadpalen list v19 Aug 2026; not manufacturer-verified and not previously in the register. Confirm against a primary source before quoting a client.</t>
+        </is>
+      </c>
+      <c r="R417" t="inlineStr">
+        <is>
+          <t>De standaard Loxone Wallbox 11kW 16A Tree staat als 'Nee / separaat'. Er bestaat ook een MID-variant. Verificatie via openbaar Loxone datasheet onvolledig – als Optie geregistreerd.
+[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Misschien'; recorded as Optional because note describes an option or variant ('als Optie').</t>
+        </is>
+      </c>
+      <c r="S417" t="inlineStr"/>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>chg_0417</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>Mennekes</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>Amtron  4you 640</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr"/>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>Integrated</t>
+        </is>
+      </c>
+      <c r="G418" t="inlineStr"/>
+      <c r="H418" t="inlineStr"/>
+      <c r="I418" t="inlineStr"/>
+      <c r="J418" t="inlineStr"/>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>Technical/Chargers/AC Chargers/Mennekes</t>
+        </is>
+      </c>
+      <c r="L418" t="inlineStr">
+        <is>
+          <t>Needs Research</t>
+        </is>
+      </c>
+      <c r="M418" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="N418" t="inlineStr"/>
+      <c r="O418" t="inlineStr"/>
+      <c r="P418" t="inlineStr"/>
+      <c r="Q418" t="inlineStr">
+        <is>
+          <t>Added 2026-08-20 from Zeres laadpalen list v19 Aug 2026; not manufacturer-verified and not previously in the register. Confirm against a primary source before quoting a client.</t>
+        </is>
+      </c>
+      <c r="R418" t="inlineStr">
+        <is>
+          <t>Wel MID meter.
+[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Ja'; recorded as Integrated because list says 'Ja' and the note does not qualify it.</t>
+        </is>
+      </c>
+      <c r="S418" t="inlineStr"/>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>chg_0418</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>NexBlue</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>Edge Max  en Delta Max</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr"/>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>Integrated</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr"/>
+      <c r="H419" t="inlineStr"/>
+      <c r="I419" t="inlineStr">
+        <is>
+          <t>https://cdn.shopify.com/s/files/1/0686/5276/1363/files/NexBlue_NexBlue_Edge_Max_Product_Sheet_EN_V2.0.pdf?v=1759911810</t>
+        </is>
+      </c>
+      <c r="J419" t="inlineStr"/>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>Technical/Chargers/AC Chargers/NexBlue</t>
+        </is>
+      </c>
+      <c r="L419" t="inlineStr">
+        <is>
+          <t>Needs Research</t>
+        </is>
+      </c>
+      <c r="M419" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="N419" t="inlineStr"/>
+      <c r="O419" t="inlineStr"/>
+      <c r="P419" t="inlineStr"/>
+      <c r="Q419" t="inlineStr">
+        <is>
+          <t>Added 2026-08-20 from Zeres laadpalen list v19 Aug 2026; not manufacturer-verified and not previously in the register. Confirm against a primary source before quoting a client.</t>
+        </is>
+      </c>
+      <c r="R419" t="inlineStr">
+        <is>
+          <t>Heeft wel een MID meter
+[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Ja'; recorded as Integrated because list says 'Ja' and the note does not qualify it.</t>
+        </is>
+      </c>
+      <c r="S419" t="inlineStr"/>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>chg_0419</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>Ohme</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>Home  of Pod</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr"/>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr"/>
+      <c r="H420" t="inlineStr"/>
+      <c r="I420" t="inlineStr"/>
+      <c r="J420" t="inlineStr"/>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>Technical/Chargers/AC Chargers/Ohme</t>
+        </is>
+      </c>
+      <c r="L420" t="inlineStr">
+        <is>
+          <t>Needs Research</t>
+        </is>
+      </c>
+      <c r="M420" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="N420" t="inlineStr"/>
+      <c r="O420" t="inlineStr"/>
+      <c r="P420" t="inlineStr"/>
+      <c r="Q420" t="inlineStr">
+        <is>
+          <t>Added 2026-08-20 from Zeres laadpalen list v19 Aug 2026; not manufacturer-verified and not previously in the register. Confirm against a primary source before quoting a client.</t>
+        </is>
+      </c>
+      <c r="R420" t="inlineStr">
+        <is>
+          <t>Geen MID meter
+[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Nee'; recorded as None because list says 'Nee' and the note does not qualify it.</t>
+        </is>
+      </c>
+      <c r="S420" t="inlineStr"/>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>chg_0420</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>Ohme</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>Home Pro</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr"/>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr"/>
+      <c r="H421" t="inlineStr"/>
+      <c r="I421" t="inlineStr">
+        <is>
+          <t>https://ohme-ev.com/nl/product/ohme-home-pro/</t>
+        </is>
+      </c>
+      <c r="J421" t="inlineStr"/>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>Technical/Chargers/AC Chargers/Ohme</t>
+        </is>
+      </c>
+      <c r="L421" t="inlineStr">
+        <is>
+          <t>Needs Research</t>
+        </is>
+      </c>
+      <c r="M421" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="N421" t="inlineStr"/>
+      <c r="O421" t="inlineStr"/>
+      <c r="P421" t="inlineStr"/>
+      <c r="Q421" t="inlineStr">
+        <is>
+          <t>Added 2026-08-20 from Zeres laadpalen list v19 Aug 2026; not manufacturer-verified and not previously in the register. Confirm against a primary source before quoting a client.</t>
+        </is>
+      </c>
+      <c r="R421" t="inlineStr">
+        <is>
+          <t>Geen MID meter.
+[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Nee'; recorded as None because list says 'Nee' and the note does not qualify it.</t>
+        </is>
+      </c>
+      <c r="S421" t="inlineStr"/>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>chg_0421</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>Ratio Electric</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>IO6</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr"/>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G422" t="inlineStr"/>
+      <c r="H422" t="inlineStr"/>
+      <c r="I422" t="inlineStr">
+        <is>
+          <t>https://www.ratio-electric.com/nl/laadpalen/</t>
+        </is>
+      </c>
+      <c r="J422" t="inlineStr"/>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>Technical/Chargers/AC Chargers/Ratio Electric</t>
+        </is>
+      </c>
+      <c r="L422" t="inlineStr">
+        <is>
+          <t>Needs Research</t>
+        </is>
+      </c>
+      <c r="M422" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="N422" t="inlineStr"/>
+      <c r="O422" t="inlineStr"/>
+      <c r="P422" t="inlineStr"/>
+      <c r="Q422" t="inlineStr">
+        <is>
+          <t>Added 2026-08-20 from Zeres laadpalen list v19 Aug 2026; not manufacturer-verified and not previously in the register. Confirm against a primary source before quoting a client.</t>
+        </is>
+      </c>
+      <c r="R422" t="inlineStr">
+        <is>
+          <t>Ratio Electric IO6 (basis) heeft geen ingebouwde MID-meter. Het serienummer: laatste 5 getallen zijn lager dan 25000
+[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Nee'; recorded as None because list says 'Nee' and the note does not qualify it.</t>
+        </is>
+      </c>
+      <c r="S422" t="inlineStr"/>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>chg_0422</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>Ratio Electric</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>IO7 Double MID</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr"/>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>Integrated</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr"/>
+      <c r="H423" t="inlineStr"/>
+      <c r="I423" t="inlineStr">
+        <is>
+          <t>https://www.ratio-electric.com/nl/laadpalen/</t>
+        </is>
+      </c>
+      <c r="J423" t="inlineStr"/>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>Technical/Chargers/AC Chargers/Ratio Electric</t>
+        </is>
+      </c>
+      <c r="L423" t="inlineStr">
+        <is>
+          <t>Needs Research</t>
+        </is>
+      </c>
+      <c r="M423" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="N423" t="inlineStr"/>
+      <c r="O423" t="inlineStr"/>
+      <c r="P423" t="inlineStr"/>
+      <c r="Q423" t="inlineStr">
+        <is>
+          <t>Added 2026-08-20 from Zeres laadpalen list v19 Aug 2026; not manufacturer-verified and not previously in the register. Confirm against a primary source before quoting a client.</t>
+        </is>
+      </c>
+      <c r="R423" t="inlineStr">
+        <is>
+          <t>Ratio Electric IO7 Double MID heeft een ingebouwde MID-gecertificeerde meter. Bevestigd via Ratio Electric productinformatie.
+[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Ja'; recorded as Integrated because list says 'Ja' and the note does not qualify it.</t>
+        </is>
+      </c>
+      <c r="S423" t="inlineStr"/>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>chg_0423</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>Schneider</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>Charge Pro</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr"/>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>Integrated</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr"/>
+      <c r="H424" t="inlineStr"/>
+      <c r="I424" t="inlineStr">
+        <is>
+          <t>Zie Zeres datasheets</t>
+        </is>
+      </c>
+      <c r="J424" t="inlineStr"/>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>Technical/Chargers/AC Chargers/Schneider</t>
+        </is>
+      </c>
+      <c r="L424" t="inlineStr">
+        <is>
+          <t>Needs Research</t>
+        </is>
+      </c>
+      <c r="M424" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="N424" t="inlineStr"/>
+      <c r="O424" t="inlineStr"/>
+      <c r="P424" t="inlineStr"/>
+      <c r="Q424" t="inlineStr">
+        <is>
+          <t>Added 2026-08-20 from Zeres laadpalen list v19 Aug 2026; not manufacturer-verified and not previously in the register. Confirm against a primary source before quoting a client.</t>
+        </is>
+      </c>
+      <c r="R424" t="inlineStr">
+        <is>
+          <t>Heeft MID meter
+[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Ja'; recorded as Integrated because list says 'Ja' and the note does not qualify it.</t>
+        </is>
+      </c>
+      <c r="S424" t="inlineStr"/>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>chg_0424</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>Shell Recharge (NewMotion)</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>Home Advanced 1.0 of 1.1</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr"/>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr"/>
+      <c r="H425" t="inlineStr"/>
+      <c r="I425" t="inlineStr"/>
+      <c r="J425" t="inlineStr"/>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>Technical/Chargers/AC Chargers/Shell Recharge (NewMotion)</t>
+        </is>
+      </c>
+      <c r="L425" t="inlineStr">
+        <is>
+          <t>Needs Research</t>
+        </is>
+      </c>
+      <c r="M425" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="N425" t="inlineStr"/>
+      <c r="O425" t="inlineStr"/>
+      <c r="P425" t="inlineStr"/>
+      <c r="Q425" t="inlineStr">
+        <is>
+          <t>Added 2026-08-20 from Zeres laadpalen list v19 Aug 2026; not manufacturer-verified and not previously in the register. Confirm against a primary source before quoting a client.</t>
+        </is>
+      </c>
+      <c r="R425" t="inlineStr">
+        <is>
+          <t>Shell Recharge / NewMotion Home Advanced 1.x heeft standaard geen ingebouwde MID-gecertificeerde meter.
+[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Nee'; recorded as None because list says 'Nee' and the note does not qualify it.</t>
+        </is>
+      </c>
+      <c r="S425" t="inlineStr"/>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>chg_0425</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>Sigenergy</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>Sigen EV AC</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr"/>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr"/>
+      <c r="H426" t="inlineStr"/>
+      <c r="I426" t="inlineStr">
+        <is>
+          <t>https://www.sigenergy.com/en/products/ac-charger</t>
+        </is>
+      </c>
+      <c r="J426" t="inlineStr"/>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>Technical/Chargers/AC Chargers/Sigenergy</t>
+        </is>
+      </c>
+      <c r="L426" t="inlineStr">
+        <is>
+          <t>Needs Research</t>
+        </is>
+      </c>
+      <c r="M426" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="N426" t="inlineStr"/>
+      <c r="O426" t="inlineStr"/>
+      <c r="P426" t="inlineStr"/>
+      <c r="Q426" t="inlineStr">
+        <is>
+          <t>Added 2026-08-20 from Zeres laadpalen list v19 Aug 2026; not manufacturer-verified and not previously in the register. Confirm against a primary source before quoting a client.</t>
+        </is>
+      </c>
+      <c r="R426" t="inlineStr">
+        <is>
+          <t>Sigenergy Sigen EV AC heeft geen MID-meter. Het NL datasheet vermeldt alleen 'Integrated metering IC', geen MID-certificering. Bevestigd via sigenergy.com NL datasheet.
+[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Nee'; recorded as None because list says 'Nee' and the note does not qualify it.</t>
+        </is>
+      </c>
+      <c r="S426" t="inlineStr"/>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>chg_0426</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>EV Charger 7.4</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr"/>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr"/>
+      <c r="H427" t="inlineStr"/>
+      <c r="I427" t="inlineStr">
+        <is>
+          <t>https://www.sma.de/en/products/e-mobility-charging-solutions/sma-ev-charger-74-22</t>
+        </is>
+      </c>
+      <c r="J427" t="inlineStr"/>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>Technical/Chargers/AC Chargers/SMA</t>
+        </is>
+      </c>
+      <c r="L427" t="inlineStr">
+        <is>
+          <t>Needs Research</t>
+        </is>
+      </c>
+      <c r="M427" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="N427" t="inlineStr"/>
+      <c r="O427" t="inlineStr"/>
+      <c r="P427" t="inlineStr"/>
+      <c r="Q427" t="inlineStr">
+        <is>
+          <t>Added 2026-08-20 from Zeres laadpalen list v19 Aug 2026; not manufacturer-verified and not previously in the register. Confirm against a primary source before quoting a client.</t>
+        </is>
+      </c>
+      <c r="R427" t="inlineStr">
+        <is>
+          <t>SMA bevestigt op eigen website: 'SMA EV Charger is implemented with an MID-compliant energy meter, but is not suitable for billing purposes'. De 7.4kW variant heeft een MID-meter maar is niet geschikt voor werkgeverdeclaratie.
+[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Ja'; recorded as Optional because note describes an option or variant ('variant heeft een MID').</t>
+        </is>
+      </c>
+      <c r="S427" t="inlineStr"/>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>chg_0427</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>Smappee</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>EV Dual</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr"/>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>Integrated</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr"/>
+      <c r="H428" t="inlineStr"/>
+      <c r="I428" t="inlineStr">
+        <is>
+          <t>https://www.smappee.com/uploads/Documentation/Technical-Documentation/EV-Dual/Smappee-Technical_specifications-EV_Dual_Wall-EN-260505.pdf</t>
+        </is>
+      </c>
+      <c r="J428" t="inlineStr"/>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>Technical/Chargers/AC Chargers/Smappee</t>
+        </is>
+      </c>
+      <c r="L428" t="inlineStr">
+        <is>
+          <t>Needs Research</t>
+        </is>
+      </c>
+      <c r="M428" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="N428" t="inlineStr"/>
+      <c r="O428" t="inlineStr"/>
+      <c r="P428" t="inlineStr"/>
+      <c r="Q428" t="inlineStr">
+        <is>
+          <t>Added 2026-08-20 from Zeres laadpalen list v19 Aug 2026; not manufacturer-verified and not previously in the register. Confirm against a primary source before quoting a client.</t>
+        </is>
+      </c>
+      <c r="R428" t="inlineStr">
+        <is>
+          <t>Smappee EV Dual heeft een ingebouwde MID-gecertificeerde energiemeter.
+[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Ja'; recorded as Integrated because list says 'Ja' and the note does not qualify it.</t>
+        </is>
+      </c>
+      <c r="S428" t="inlineStr"/>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>chg_0428</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>Smappe</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>UV Ultra</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr"/>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr"/>
+      <c r="H429" t="inlineStr"/>
+      <c r="I429" t="inlineStr">
+        <is>
+          <t>Zie Zeres docs</t>
+        </is>
+      </c>
+      <c r="J429" t="inlineStr"/>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>Technical/Chargers/AC Chargers/Smappe</t>
+        </is>
+      </c>
+      <c r="L429" t="inlineStr">
+        <is>
+          <t>Needs Research</t>
+        </is>
+      </c>
+      <c r="M429" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="N429" t="inlineStr"/>
+      <c r="O429" t="inlineStr"/>
+      <c r="P429" t="inlineStr"/>
+      <c r="Q429" t="inlineStr">
+        <is>
+          <t>Added 2026-08-20 from Zeres laadpalen list v19 Aug 2026; not manufacturer-verified and not previously in the register. Confirm against a primary source before quoting a client.</t>
+        </is>
+      </c>
+      <c r="R429" t="inlineStr">
+        <is>
+          <t>Geen MID meter
+[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Nee'; recorded as None because list says 'Nee' and the note does not qualify it.</t>
+        </is>
+      </c>
+      <c r="S429" t="inlineStr"/>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>chg_0429</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>SolarEdge</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>EV Charger (oud model)</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr"/>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr"/>
+      <c r="H430" t="inlineStr"/>
+      <c r="I430" t="inlineStr">
+        <is>
+          <t>https://knowledge-center.solaredge.com/sites/kc/files/se-ev-charger-datasheet-eu.pdf</t>
+        </is>
+      </c>
+      <c r="J430" t="inlineStr"/>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>Technical/Chargers/AC Chargers/SolarEdge</t>
+        </is>
+      </c>
+      <c r="L430" t="inlineStr">
+        <is>
+          <t>Needs Research</t>
+        </is>
+      </c>
+      <c r="M430" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="N430" t="inlineStr"/>
+      <c r="O430" t="inlineStr"/>
+      <c r="P430" t="inlineStr"/>
+      <c r="Q430" t="inlineStr">
+        <is>
+          <t>Added 2026-08-20 from Zeres laadpalen list v19 Aug 2026; not manufacturer-verified and not previously in the register. Confirm against a primary source before quoting a client.</t>
+        </is>
+      </c>
+      <c r="R430" t="inlineStr">
+        <is>
+          <t>SolarEdge EV Charger (oud model SE-EVK22) heeft MID als optie (nauwkeurigheidsklasse B). Niet standaard ingebouwd.
+[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Misschien'; recorded as Optional because note describes an option or variant ('als optie').</t>
+        </is>
+      </c>
+      <c r="S430" t="inlineStr"/>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>chg_0430</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>SolarEdge</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>ONE EV Charger Pro (SE-EVN22P)</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr"/>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>Integrated</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr"/>
+      <c r="H431" t="inlineStr"/>
+      <c r="I431" t="inlineStr">
+        <is>
+          <t>https://knowledge-center.solaredge.com/sites/kc/files/se-ev-charger-datasheet-eu.pdf</t>
+        </is>
+      </c>
+      <c r="J431" t="inlineStr"/>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>Technical/Chargers/AC Chargers/SolarEdge</t>
+        </is>
+      </c>
+      <c r="L431" t="inlineStr">
+        <is>
+          <t>Needs Research</t>
+        </is>
+      </c>
+      <c r="M431" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="N431" t="inlineStr"/>
+      <c r="O431" t="inlineStr"/>
+      <c r="P431" t="inlineStr"/>
+      <c r="Q431" t="inlineStr">
+        <is>
+          <t>Added 2026-08-20 from Zeres laadpalen list v19 Aug 2026; not manufacturer-verified and not previously in the register. Confirm against a primary source before quoting a client.</t>
+        </is>
+      </c>
+      <c r="R431" t="inlineStr">
+        <is>
+          <t>Het nieuwere SolarEdge ONE EV Charger Pro model heeft een standaard ingebouwde MID-gecertificeerde meter. Bevestigd via SolarEdge EU datasheet.
+[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Ja'; recorded as Integrated because list says 'Ja' and the note does not qualify it.</t>
+        </is>
+      </c>
+      <c r="S431" t="inlineStr"/>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>chg_0431</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>SolarLife</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>1 model bekend</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr"/>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>Integrated</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr"/>
+      <c r="H432" t="inlineStr"/>
+      <c r="I432" t="inlineStr">
+        <is>
+          <t>https://wedrivesolar.com/nl/solar-life/</t>
+        </is>
+      </c>
+      <c r="J432" t="inlineStr"/>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>Technical/Chargers/AC Chargers/SolarLife</t>
+        </is>
+      </c>
+      <c r="L432" t="inlineStr">
+        <is>
+          <t>Needs Research</t>
+        </is>
+      </c>
+      <c r="M432" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="N432" t="inlineStr"/>
+      <c r="O432" t="inlineStr"/>
+      <c r="P432" t="inlineStr"/>
+      <c r="Q432" t="inlineStr">
+        <is>
+          <t>Added 2026-08-20 from Zeres laadpalen list v19 Aug 2026; not manufacturer-verified and not previously in the register. Confirm against a primary source before quoting a client.</t>
+        </is>
+      </c>
+      <c r="R432" t="inlineStr">
+        <is>
+          <t>Heeft een MID meter, er is 1 model bekend zonder modelnaam.
+[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Ja'; recorded as Integrated because list says 'Ja' and the note does not qualify it.</t>
+        </is>
+      </c>
+      <c r="S432" t="inlineStr"/>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>chg_0432</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>Spelsberg</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>Wallbox</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr"/>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>Integrated</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr"/>
+      <c r="H433" t="inlineStr"/>
+      <c r="I433" t="inlineStr">
+        <is>
+          <t>https://www.spelsberg.de/produktprogramm/e-mobility/</t>
+        </is>
+      </c>
+      <c r="J433" t="inlineStr"/>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>Technical/Chargers/AC Chargers/Spelsberg</t>
+        </is>
+      </c>
+      <c r="L433" t="inlineStr">
+        <is>
+          <t>Needs Research</t>
+        </is>
+      </c>
+      <c r="M433" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="N433" t="inlineStr"/>
+      <c r="O433" t="inlineStr"/>
+      <c r="P433" t="inlineStr"/>
+      <c r="Q433" t="inlineStr">
+        <is>
+          <t>Added 2026-08-20 from Zeres laadpalen list v19 Aug 2026; not manufacturer-verified and not previously in the register. Confirm against a primary source before quoting a client.</t>
+        </is>
+      </c>
+      <c r="R433" t="inlineStr">
+        <is>
+          <t>Spelsberg Wallbox heeft een ingebouwde MID-gecertificeerde energiemeter. Bevestigd via Spelsberg productdatasheet.
+[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Ja'; recorded as Integrated because list says 'Ja' and the note does not qualify it.</t>
+        </is>
+      </c>
+      <c r="S433" t="inlineStr"/>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>chg_0433</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>Sunpower</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>Drive AC Charger</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr"/>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr"/>
+      <c r="H434" t="inlineStr"/>
+      <c r="I434" t="inlineStr">
+        <is>
+          <t>https://sunpower.maxeon.com/</t>
+        </is>
+      </c>
+      <c r="J434" t="inlineStr"/>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>Technical/Chargers/AC Chargers/Sunpower</t>
+        </is>
+      </c>
+      <c r="L434" t="inlineStr">
+        <is>
+          <t>Needs Research</t>
+        </is>
+      </c>
+      <c r="M434" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="N434" t="inlineStr"/>
+      <c r="O434" t="inlineStr"/>
+      <c r="P434" t="inlineStr"/>
+      <c r="Q434" t="inlineStr">
+        <is>
+          <t>Added 2026-08-20 from Zeres laadpalen list v19 Aug 2026; not manufacturer-verified and not previously in the register. Confirm against a primary source before quoting a client.</t>
+        </is>
+      </c>
+      <c r="R434" t="inlineStr">
+        <is>
+          <t>SunPower Drive AC Charger heeft geen ingebouwde MID-meter. Geen MID vermeld in productspecificaties. ZERES
+[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Nee'; recorded as None because list says 'Nee' and the note does not qualify it.</t>
+        </is>
+      </c>
+      <c r="S434" t="inlineStr"/>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>chg_0434</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>Tesla</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>Wall Connector Generation 1</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr"/>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="G435" t="inlineStr"/>
+      <c r="H435" t="inlineStr"/>
+      <c r="I435" t="inlineStr">
+        <is>
+          <t>https://www.tesla.com/en_nl/support/home-charging-installation/wall-connector</t>
+        </is>
+      </c>
+      <c r="J435" t="inlineStr"/>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>Technical/Chargers/AC Chargers/Tesla</t>
+        </is>
+      </c>
+      <c r="L435" t="inlineStr">
+        <is>
+          <t>Needs Research</t>
+        </is>
+      </c>
+      <c r="M435" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="N435" t="inlineStr"/>
+      <c r="O435" t="inlineStr"/>
+      <c r="P435" t="inlineStr"/>
+      <c r="Q435" t="inlineStr">
+        <is>
+          <t>Added 2026-08-20 from Zeres laadpalen list v19 Aug 2026; not manufacturer-verified and not previously in the register. Confirm against a primary source before quoting a client.</t>
+        </is>
+      </c>
+      <c r="R435" t="inlineStr">
+        <is>
+          <t>Tesla Wall Connector Gen 1 heeft geen MID-meter. MID was een tijdelijk beschikbare optie maar is niet standaard aanwezig.
+[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Nee'; recorded as Optional because note describes an option or variant ('MID was een tijdelijk beschikbare optie').</t>
+        </is>
+      </c>
+      <c r="S435" t="inlineStr"/>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>chg_0435</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>Tesla</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>Wall Connector Generation 2</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr"/>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="G436" t="inlineStr"/>
+      <c r="H436" t="inlineStr"/>
+      <c r="I436" t="inlineStr">
+        <is>
+          <t>https://www.tesla.com/en_nl/support/home-charging-installation/wall-connector</t>
+        </is>
+      </c>
+      <c r="J436" t="inlineStr"/>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>Technical/Chargers/AC Chargers/Tesla</t>
+        </is>
+      </c>
+      <c r="L436" t="inlineStr">
+        <is>
+          <t>Needs Research</t>
+        </is>
+      </c>
+      <c r="M436" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="N436" t="inlineStr"/>
+      <c r="O436" t="inlineStr"/>
+      <c r="P436" t="inlineStr"/>
+      <c r="Q436" t="inlineStr">
+        <is>
+          <t>Added 2026-08-20 from Zeres laadpalen list v19 Aug 2026; not manufacturer-verified and not previously in the register. Confirm against a primary source before quoting a client.</t>
+        </is>
+      </c>
+      <c r="R436" t="inlineStr">
+        <is>
+          <t>Tesla Wall Connector Gen 2 heeft geen MID-meter. MID was een tijdelijk beschikbare optie maar is niet standaard aanwezig.
+[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Nee'; recorded as Optional because note describes an option or variant ('MID was een tijdelijk beschikbare optie').</t>
+        </is>
+      </c>
+      <c r="S436" t="inlineStr"/>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>chg_0436</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>Tesla</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>Wall Connector Generation 3</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr"/>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G437" t="inlineStr"/>
+      <c r="H437" t="inlineStr"/>
+      <c r="I437" t="inlineStr">
+        <is>
+          <t>https://www.anwb.nl/auto/elektrisch-rijden/laadpalen/tesla-laadpaal-review</t>
+        </is>
+      </c>
+      <c r="J437" t="inlineStr"/>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>Technical/Chargers/AC Chargers/Tesla</t>
+        </is>
+      </c>
+      <c r="L437" t="inlineStr">
+        <is>
+          <t>Needs Research</t>
+        </is>
+      </c>
+      <c r="M437" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="N437" t="inlineStr"/>
+      <c r="O437" t="inlineStr"/>
+      <c r="P437" t="inlineStr"/>
+      <c r="Q437" t="inlineStr">
+        <is>
+          <t>Added 2026-08-20 from Zeres laadpalen list v19 Aug 2026; not manufacturer-verified and not previously in the register. Confirm against a primary source before quoting a client.</t>
+        </is>
+      </c>
+      <c r="R437" t="inlineStr">
+        <is>
+          <t>Tesla Wall Connector Gen 3 is beschikbaar in twee varianten: zonder MID en met MID-gecertificeerde meter. Controleer uw factuur of App of er een MID meter in aanwezig is.
+[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Nee'; recorded as None because list says 'Nee' and the note does not qualify it.</t>
+        </is>
+      </c>
+      <c r="S437" t="inlineStr"/>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>chg_0437</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>Tesla</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>Wall Connector Generation 3 MID</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr"/>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>Integrated</t>
+        </is>
+      </c>
+      <c r="G438" t="inlineStr"/>
+      <c r="H438" t="inlineStr"/>
+      <c r="I438" t="inlineStr">
+        <is>
+          <t>Wall Connector Generation 3</t>
+        </is>
+      </c>
+      <c r="J438" t="inlineStr"/>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>Technical/Chargers/AC Chargers/Tesla</t>
+        </is>
+      </c>
+      <c r="L438" t="inlineStr">
+        <is>
+          <t>Needs Research</t>
+        </is>
+      </c>
+      <c r="M438" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="N438" t="inlineStr"/>
+      <c r="O438" t="inlineStr"/>
+      <c r="P438" t="inlineStr"/>
+      <c r="Q438" t="inlineStr">
+        <is>
+          <t>Added 2026-08-20 from Zeres laadpalen list v19 Aug 2026; not manufacturer-verified and not previously in the register. Confirm against a primary source before quoting a client.</t>
+        </is>
+      </c>
+      <c r="R438" t="inlineStr">
+        <is>
+          <t>Deze Wallconnector heeft wel een MID meter
+[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Ja'; recorded as Integrated because list says 'Ja' and the note does not qualify it.</t>
+        </is>
+      </c>
+      <c r="S438" t="inlineStr"/>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>chg_0438</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>Tinkerforge</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>WARP3</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr"/>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>Integrated</t>
+        </is>
+      </c>
+      <c r="G439" t="inlineStr"/>
+      <c r="H439" t="inlineStr"/>
+      <c r="I439" t="inlineStr">
+        <is>
+          <t>https://shop.tinkerforge.com/en/warp/wallbox/warp3-charger-pro-powder-coated.html</t>
+        </is>
+      </c>
+      <c r="J439" t="inlineStr"/>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>Technical/Chargers/AC Chargers/Tinkerforge</t>
+        </is>
+      </c>
+      <c r="L439" t="inlineStr">
+        <is>
+          <t>Needs Research</t>
+        </is>
+      </c>
+      <c r="M439" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="N439" t="inlineStr"/>
+      <c r="O439" t="inlineStr"/>
+      <c r="P439" t="inlineStr"/>
+      <c r="Q439" t="inlineStr">
+        <is>
+          <t>Added 2026-08-20 from Zeres laadpalen list v19 Aug 2026; not manufacturer-verified and not previously in the register. Confirm against a primary source before quoting a client.</t>
+        </is>
+      </c>
+      <c r="R439" t="inlineStr">
+        <is>
+          <t>Nieuwe Duitse laadpaal met MID meter.
+[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Ja'; recorded as Integrated because list says 'Ja' and the note does not qualify it.</t>
+        </is>
+      </c>
+      <c r="S439" t="inlineStr"/>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>chg_0439</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>van Mossel Energie</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>11, 22 kW OneCharge</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr"/>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>Integrated</t>
+        </is>
+      </c>
+      <c r="G440" t="inlineStr"/>
+      <c r="H440" t="inlineStr"/>
+      <c r="I440" t="inlineStr">
+        <is>
+          <t>https://www.vanmossel.nl/energie-thuis/thuis/laadpalen.</t>
+        </is>
+      </c>
+      <c r="J440" t="inlineStr"/>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>Technical/Chargers/AC Chargers/van Mossel Energie</t>
+        </is>
+      </c>
+      <c r="L440" t="inlineStr">
+        <is>
+          <t>Needs Research</t>
+        </is>
+      </c>
+      <c r="M440" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="N440" t="inlineStr"/>
+      <c r="O440" t="inlineStr"/>
+      <c r="P440" t="inlineStr"/>
+      <c r="Q440" t="inlineStr">
+        <is>
+          <t>Added 2026-08-20 from Zeres laadpalen list v19 Aug 2026; not manufacturer-verified and not previously in the register. Confirm against a primary source before quoting a client.</t>
+        </is>
+      </c>
+      <c r="R440" t="inlineStr">
+        <is>
+          <t>MID meter in alle modellen volgens de website van van Mossel ENergie (vaak Peblar)
+[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Ja'; recorded as Integrated because list says 'Ja' and the note does not qualify it.</t>
+        </is>
+      </c>
+      <c r="S440" t="inlineStr"/>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>chg_0440</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>Vestel (Amazon)</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>Wallbox EVC04-AC11-11 kW</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr"/>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="G441" t="inlineStr"/>
+      <c r="H441" t="inlineStr"/>
+      <c r="I441" t="inlineStr">
+        <is>
+          <t>https://www.vestel-echarger.com/</t>
+        </is>
+      </c>
+      <c r="J441" t="inlineStr"/>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>Technical/Chargers/AC Chargers/Vestel (Amazon)</t>
+        </is>
+      </c>
+      <c r="L441" t="inlineStr">
+        <is>
+          <t>Needs Research</t>
+        </is>
+      </c>
+      <c r="M441" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="N441" t="inlineStr"/>
+      <c r="O441" t="inlineStr"/>
+      <c r="P441" t="inlineStr"/>
+      <c r="Q441" t="inlineStr">
+        <is>
+          <t>Added 2026-08-20 from Zeres laadpalen list v19 Aug 2026; not manufacturer-verified and not previously in the register. Confirm against a primary source before quoting a client.</t>
+        </is>
+      </c>
+      <c r="R441" t="inlineStr">
+        <is>
+          <t>Vestel EVC04-AC11 heeft geen ingebouwde MID-meter. Bevestigd via productspecificaties; MID was optie bij een oudere versie.
+[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Nee'; recorded as Optional because note describes an option or variant ('MID was optie').</t>
+        </is>
+      </c>
+      <c r="S441" t="inlineStr"/>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>chg_0441</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>Volkswagen</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>ID. Charger Pro</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr"/>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>Integrated</t>
+        </is>
+      </c>
+      <c r="G442" t="inlineStr"/>
+      <c r="H442" t="inlineStr"/>
+      <c r="I442" t="inlineStr">
+        <is>
+          <t>https://www.volkswagen.co.uk/en/electric/charging-and-range/id-charger.html</t>
+        </is>
+      </c>
+      <c r="J442" t="inlineStr"/>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>Technical/Chargers/AC Chargers/Volkswagen</t>
+        </is>
+      </c>
+      <c r="L442" t="inlineStr">
+        <is>
+          <t>Needs Research</t>
+        </is>
+      </c>
+      <c r="M442" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="N442" t="inlineStr"/>
+      <c r="O442" t="inlineStr"/>
+      <c r="P442" t="inlineStr"/>
+      <c r="Q442" t="inlineStr">
+        <is>
+          <t>Added 2026-08-20 from Zeres laadpalen list v19 Aug 2026; not manufacturer-verified and not previously in the register. Confirm against a primary source before quoting a client.</t>
+        </is>
+      </c>
+      <c r="R442" t="inlineStr">
+        <is>
+          <t>Volkswagen ID. Charger Pro heeft een ingebouwde MID-gecertificeerde elektriciteitsmeter. Bevestigd via officiële Volkswagen UK productpagina. Geldt uitdrukkelijk alleen voor het Pro-model.
+[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Ja'; recorded as Integrated because list says 'Ja' and the note does not qualify it.</t>
+        </is>
+      </c>
+      <c r="S442" t="inlineStr"/>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>chg_0442</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>Voldt</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>Mobile OCPP Charger</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr"/>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>Integrated</t>
+        </is>
+      </c>
+      <c r="G443" t="inlineStr"/>
+      <c r="H443" t="inlineStr"/>
+      <c r="I443" t="inlineStr">
+        <is>
+          <t>https://voldt.be/cdn/shop/files/voldt-smart-charger-brochure-dutch-final.pdf?v=3854672458710497402</t>
+        </is>
+      </c>
+      <c r="J443" t="inlineStr"/>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>Technical/Chargers/AC Chargers/Voldt</t>
+        </is>
+      </c>
+      <c r="L443" t="inlineStr">
+        <is>
+          <t>Needs Research</t>
+        </is>
+      </c>
+      <c r="M443" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="N443" t="inlineStr"/>
+      <c r="O443" t="inlineStr"/>
+      <c r="P443" t="inlineStr"/>
+      <c r="Q443" t="inlineStr">
+        <is>
+          <t>Added 2026-08-20 from Zeres laadpalen list v19 Aug 2026; not manufacturer-verified and not previously in the register. Confirm against a primary source before quoting a client.</t>
+        </is>
+      </c>
+      <c r="R443" t="inlineStr">
+        <is>
+          <t>Dit model heeft MID meter ingebouwd.
+[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Ja'; recorded as Integrated because list says 'Ja' and the note does not qualify it.</t>
+        </is>
+      </c>
+      <c r="S443" t="inlineStr"/>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>chg_0443</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>Volvo</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>Wallbox GHO22E21</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr"/>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>Integrated</t>
+        </is>
+      </c>
+      <c r="G444" t="inlineStr"/>
+      <c r="H444" t="inlineStr"/>
+      <c r="I444" t="inlineStr">
+        <is>
+          <t>https://www.volvocars.com/nl-be/shop/additionals/volvo-wallbox-with-socket-mid/</t>
+        </is>
+      </c>
+      <c r="J444" t="inlineStr"/>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>Technical/Chargers/AC Chargers/Volvo</t>
+        </is>
+      </c>
+      <c r="L444" t="inlineStr">
+        <is>
+          <t>Needs Research</t>
+        </is>
+      </c>
+      <c r="M444" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="N444" t="inlineStr"/>
+      <c r="O444" t="inlineStr"/>
+      <c r="P444" t="inlineStr"/>
+      <c r="Q444" t="inlineStr">
+        <is>
+          <t>Added 2026-08-20 from Zeres laadpalen list v19 Aug 2026; not manufacturer-verified and not previously in the register. Confirm against a primary source before quoting a client.</t>
+        </is>
+      </c>
+      <c r="R444" t="inlineStr">
+        <is>
+          <t>Volvo Wallbox (model GHO22E213A en varianten) heeft een ingebouwde MID-gecertificeerde energiemeter. Bevestigd via Volvo Cars NL pagina: 'Gekalibreerd overeenkomstig het MID-certificaat'.
+[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Ja'; recorded as Integrated because list says 'Ja' and the note does not qualify it.</t>
+        </is>
+      </c>
+      <c r="S444" t="inlineStr"/>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>chg_0444</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>Wallbox</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>Pulsar Pro MID</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr"/>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>Integrated</t>
+        </is>
+      </c>
+      <c r="G445" t="inlineStr"/>
+      <c r="H445" t="inlineStr"/>
+      <c r="I445" t="inlineStr"/>
+      <c r="J445" t="inlineStr"/>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>Technical/Chargers/AC Chargers/Wallbox</t>
+        </is>
+      </c>
+      <c r="L445" t="inlineStr">
+        <is>
+          <t>Needs Research</t>
+        </is>
+      </c>
+      <c r="M445" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="N445" t="inlineStr"/>
+      <c r="O445" t="inlineStr"/>
+      <c r="P445" t="inlineStr"/>
+      <c r="Q445" t="inlineStr">
+        <is>
+          <t>Added 2026-08-20 from Zeres laadpalen list v19 Aug 2026; not manufacturer-verified and not previously in the register. Confirm against a primary source before quoting a client.</t>
+        </is>
+      </c>
+      <c r="R445" t="inlineStr">
+        <is>
+          <t>NIeuw model vanaf 2026: aantonen met een factuur dat het de nieuw Pulsar Pro is met MID meter.
+[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Ja'; recorded as Integrated because list says 'Ja' and the note does not qualify it.</t>
+        </is>
+      </c>
+      <c r="S445" t="inlineStr"/>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>chg_0445</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>WissEnergy</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>Alle typen</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr"/>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="G446" t="inlineStr"/>
+      <c r="H446" t="inlineStr"/>
+      <c r="I446" t="inlineStr">
+        <is>
+          <t>https://www.wissenergy.com/</t>
+        </is>
+      </c>
+      <c r="J446" t="inlineStr"/>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>Technical/Chargers/AC Chargers/WissEnergy</t>
+        </is>
+      </c>
+      <c r="L446" t="inlineStr">
+        <is>
+          <t>Needs Research</t>
+        </is>
+      </c>
+      <c r="M446" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="N446" t="inlineStr"/>
+      <c r="O446" t="inlineStr"/>
+      <c r="P446" t="inlineStr"/>
+      <c r="Q446" t="inlineStr">
+        <is>
+          <t>Added 2026-08-20 from Zeres laadpalen list v19 Aug 2026; not manufacturer-verified and not previously in the register. Confirm against a primary source before quoting a client.</t>
+        </is>
+      </c>
+      <c r="R446" t="inlineStr">
+        <is>
+          <t>WissEnergy laadpalen hebben geen ingebouwde MID-meter; MID is optie. Bevestigd via WissEnergy productinformatie.
+[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Nee'; recorded as Optional because note describes an option or variant ('MID is optie').</t>
+        </is>
+      </c>
+      <c r="S446" t="inlineStr"/>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>chg_0446</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>Zappi (Myenergi)</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr"/>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G447" t="inlineStr"/>
+      <c r="H447" t="inlineStr"/>
+      <c r="I447" t="inlineStr">
+        <is>
+          <t>Zappi-2.1-T-EU_Datasheet_NL.pdf</t>
+        </is>
+      </c>
+      <c r="J447" t="inlineStr"/>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>Technical/Chargers/AC Chargers/Zappi (Myenergi)</t>
+        </is>
+      </c>
+      <c r="L447" t="inlineStr">
+        <is>
+          <t>Needs Research</t>
+        </is>
+      </c>
+      <c r="M447" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="N447" t="inlineStr"/>
+      <c r="O447" t="inlineStr"/>
+      <c r="P447" t="inlineStr"/>
+      <c r="Q447" t="inlineStr">
+        <is>
+          <t>Added 2026-08-20 from Zeres laadpalen list v19 Aug 2026; not manufacturer-verified and not previously in the register. Confirm against a primary source before quoting a client.</t>
+        </is>
+      </c>
+      <c r="R447" t="inlineStr">
+        <is>
+          <t>Geen MID meter
+[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Nee'; recorded as None because list says 'Nee' and the note does not qualify it.</t>
+        </is>
+      </c>
+      <c r="S447" t="inlineStr"/>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>chg_0447</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>Zonneplan</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>Charge en Charge 2</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr"/>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G448" t="inlineStr"/>
+      <c r="H448" t="inlineStr"/>
+      <c r="I448" t="inlineStr"/>
+      <c r="J448" t="inlineStr"/>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>Technical/Chargers/AC Chargers/Zonneplan</t>
+        </is>
+      </c>
+      <c r="L448" t="inlineStr">
+        <is>
+          <t>Needs Research</t>
+        </is>
+      </c>
+      <c r="M448" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="N448" t="inlineStr"/>
+      <c r="O448" t="inlineStr"/>
+      <c r="P448" t="inlineStr"/>
+      <c r="Q448" t="inlineStr">
+        <is>
+          <t>Added 2026-08-20 from Zeres laadpalen list v19 Aug 2026; not manufacturer-verified and not previously in the register. Confirm against a primary source before quoting a client.</t>
+        </is>
+      </c>
+      <c r="R448" t="inlineStr">
+        <is>
+          <t>Zonneplan bevestigt zelf op de website dat de Charge en Charge 2 GEEN MID-meter hebben en daarmee niet in aanmerking komen voor ERE-certificaten.
+[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Nee'; recorded as None because list says 'Nee' and the note does not qualify it.</t>
+        </is>
+      </c>
+      <c r="S448" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -27502,7 +31901,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:N28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -27510,13 +31909,15 @@
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="60" customWidth="1" min="9" max="9"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="60" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -27542,44 +31943,1697 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Source A</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Source B</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Tracker says</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Tracker note</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Zite says</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Zite original value</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Zite note</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Decision</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Decided By</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Decided At</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>cfl_0001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>chg_0024</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ABL (=Wallbox)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>emH4</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>MID Register</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Integrated</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>MID standard in + variants
+[migrated 2026-08-18] Seed MID Status was 'Yes'; migrated to 'Integrated' because seed value 'Yes' mapped directly. Original seed source: zeres.nl/laadpaal-check MID-meter list.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>ABL eMH2 heeft een ingebouwde MID-gecertificeerde meter in de + varianten. Bevestigd via ABL FAQ: 'MID meter is standaard aanwezig bij eMH2+ en eMH3+ varianten'. [read as Optional: note describes an option or variant ('MID-gecertificeerde meter in de + variant')]</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>cfl_0002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>chg_0025</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ABL (=Wallbox)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>emH5</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>MID Register</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Integrated</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>MID in + variants
+[migrated 2026-08-18] Seed MID Status was 'Yes'; migrated to 'Integrated' because seed value 'Yes' mapped directly. Original seed source: zeres.nl/laadpaal-check MID-meter list.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>ABL eMH3 heeft een ingebouwde MID-gecertificeerde meter in de + varianten. Bevestigd via ABL FAQ. [read as Optional: note describes an option or variant ('MID-gecertificeerde meter in de + variant')]</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>cfl_0003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>chg_0039</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Autel</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>MaxiCharger AC Elite</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>MID Register</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>No European MID certification | Real Autel product but NEMA/UL/CSA-certified North America market model -- no evidence of EU distribution found. Likely a seed-data region error.
+[migrated 2026-08-18] Seed MID Status was 'N/A'; migrated to 'Unknown' because seed value 'N/A' mapped directly. Original seed source: Autel US (autelenergy.us).</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Nee</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Autel MaxiCharger AC Elite heeft geen Europese MID-certificering. Bevestigd via autelenergy.eu en laadnet.nl. [read as None: list says 'Nee' and the note does not qualify it]</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>cfl_0004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>chg_0038</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Autel</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>MaxiCharger AC Compact</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>MID Register</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>No European MID certification | Confirmed real current EU model. Datasheet only states 'Power measurement accuracy +/-2.0%' -- no explicit 'MID' wording, unlike the AC Wallbox sheet. Treat as unconfirmed pending official EU spec sheet.
+[migrated 2026-08-18] Seed MID Status was 'Maybe'; migrated to 'Optional' because seed value 'Maybe' mapped directly. Original seed source: Autel EU via UK distributor Thundergrid.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Nee</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Autel MaxiCharger AC Compact heeft geen Europese MID-certificering. Bevestigd via autelenergy.eu. [read as None: list says 'Nee' and the note does not qualify it]</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>cfl_0005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>chg_0056</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Blue Current</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Nano XL</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>MID Register</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Built-in MID meter | Blue Current's public/commercial charging variant ('Openbaar laden 2.0'). Not individually confirmed for MID but covered by the brand's general 'all charge points have MID meter' statement. NOTE: a claimed CubeCharging business-line transfer to Blue Current (raised during Cube's research) could NOT be corroborated on either company's site -- treat as unverified, no evidence of shared/rebadged hardware found.
+[migrated 2026-08-18] Seed MID Status was 'Maybe'; migrated to 'Optional' because seed value 'Maybe' mapped directly. Original seed source: HELAF Elektrotechniek (ins</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Integrated</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Blue Current Nano XL heeft een MID-meter .  Bevestigd via Blue Current productsheet. [read as Integrated: list says 'Ja' and the note does not qualify it]</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>cfl_0006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>chg_0079</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ChargeAmps</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Aura</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>MID Register</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Built-in MID meter | CORRECTION vs seed (was confident 'Yes'): datasheet phrasing is 'equivalent to the Measuring Instruments Directive 2014/32/EU' -- NOT an explicit 'certified MID meter' claim like Dawn uses. Downgraded to Maybe pending direct manufacturer confirmation.
+[migrated 2026-08-18] Seed MID Status was 'Maybe'; migrated to 'Optional' because seed value 'Maybe' mapped directly. Original seed source: ChargeAmps official (chargeamps.com).</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Integrated</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>ChargeAmps Aura heeft een ingebouwde MID-gecertificeerde meter. Bevestigd via ChargeAmps productinformatie. [read as Integrated: list says 'Ja' and the note does not qualify it]</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>cfl_0007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>chg_0084</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ChargeAmps</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Luna</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>MID Register</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>No built-in MID meter | CORRECTION vs seed (was confident 'No'): datasheet makes NO mention of MID/EN 50470 at all (not even as absent/optional) -- changed to Unknown pending direct confirmation, distinguishing it from Halo/Aura's ambiguous phrasing and Dawn's explicit certification.
+[migrated 2026-08-18] Seed MID Status was 'Unknown'; migrated to 'Unknown' because seed value 'Unknown' but the notes rule out the MID option they mention — seed and notes disagree, so this is not established. Original seed source: ChargeAmps official (chargeamps.com).</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Nee</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>ChargeAmps Luna heeft geen ingebouwde MID-meter. Bevestigd via ChargeAmps productinformatie. [read as None: list says 'Nee' and the note does not qualify it]</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>cfl_0008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>chg_0151</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>EVBox</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Livo</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>MID Register</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>No MID certification | IMPORTANT CONTEXT: EVBox Group was shut down by parent Engie in Oct 2024 (~EUR800M losses). AC business (Elvi/Livo/Liviqo/BusinessLine) is now wind-down/after-sales-only via evaftersales.com, NOT actively sold. Livo page states meter 'Class A accuracy +/-2%, EN 50470-3' (MID-relevant standard) but page access was blocked (403) this round so exact MID wording unconfirmed — hence Maybe not Yes.
+[migrated 2026-08-18] Seed MID Status was 'Maybe'; migrated to 'Unknown' because seed value 'Maybe' but the notes state 'No MID' — the evidence points both ways, so this is not est</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Nee</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>EVBox Livo heeft geen MID-gecertificeerde meter. De datasheet vermeldt alleen 'Class A kWh meter' zonder MID-certificering. Bevestigd via laadnet.nl: Livo staat niet op de ERE-compatibele lijst. [read as None: list says 'Nee' and the note does not qualify it]</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>cfl_0009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>chg_0182</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Grasen</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>EV Wallcharger</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>MID Register</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>No MID meter | DATA QUALITY WARNING: manufacturer Luoyang Grasen Power Technology Co., Ltd. runs 3 parallel marketing domains (grasen.com, grasencharge.com, grasen-power.com) publishing near-identical 7/11/22kW AC wallbox specs under half a dozen SEO landing-page names ('EV Wall Charger', 'Home EV Charger', '7kW Home Charger', 'Level 2 EV Charger', generic 'AC EV Charger') -- these appear to be 1-2 real underlying SKUs, not distinct products. MID is inconsistently advertised across these pages even for what may be the same physical unit -- treat as 'MID available as an option, inconsistently m</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Nee</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>[read as None: list says 'Nee' and the note does not qualify it]</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>cfl_0010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>chg_0184</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Grasen</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Level 2 Charger</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>MID Register</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Built-in MID meter | DATA QUALITY WARNING: manufacturer Luoyang Grasen Power Technology Co., Ltd. runs 3 parallel marketing domains (grasen.com, grasencharge.com, grasen-power.com) publishing near-identical 7/11/22kW AC wallbox specs under half a dozen SEO landing-page names ('EV Wall Charger', 'Home EV Charger', '7kW Home Charger', 'Level 2 EV Charger', generic 'AC EV Charger') -- these appear to be 1-2 real underlying SKUs, not distinct products. MID is inconsistently advertised across these pages even for what may be the same physical unit -- treat as 'MID available as an option, inconsiste</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Integrated</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>MID meter ingebouwd [read as Integrated: list says 'Ja' and the note does not qualify it]</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>cfl_0011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>chg_0183</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Grasen</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Home Charger</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>MID Register</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>No MID meter | DATA QUALITY WARNING: manufacturer Luoyang Grasen Power Technology Co., Ltd. runs 3 parallel marketing domains (grasen.com, grasencharge.com, grasen-power.com) publishing near-identical 7/11/22kW AC wallbox specs under half a dozen SEO landing-page names ('EV Wall Charger', 'Home EV Charger', '7kW Home Charger', 'Level 2 EV Charger', generic 'AC EV Charger') -- these appear to be 1-2 real underlying SKUs, not distinct products. MID is inconsistently advertised across these pages even for what may be the same physical unit -- treat as 'MID available as an option, inconsistently m</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Nee</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>[read as None: list says 'Nee' and the note does not qualify it]</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>cfl_0012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>chg_0186</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Hager</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>witty park 2</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>MID Register</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>No built-in MID meter | CORRECTION vs seed (was No): datasheet explicitly states 'deux compteurs MID' (two MID meters, one per charging point). Dual 22kW public/tertiary parking product.
+[migrated 2026-08-18] Seed MID Status was 'Yes'; migrated to 'Unknown' because seed value 'Yes' but the notes state 'No built-in MID' — the evidence points both ways, so this is not established. Original seed source: Hager official (assets.hager.com).</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Nee</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Hager Witty Park 2 heeft geen ingebouwde MID-meter. Bevestigd via Hager productinformatie. [read as None: list says 'Nee' and the note does not qualify it]</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>cfl_0013</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>chg_0202</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>KEBA</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>P30 PV</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>MID Register</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>External</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Built-in MID meter | CORRECTION vs. Zeres seed data: official KEBA comparison table shows the 'MID-certified' and 'German calibration law (ME)' rows as BLANK for PV Edition — it has NO built-in MID meter (works with an external KeContact E10 Smart Energy Meter for solar-surplus detection only, not for billing). Source: https://www.keba.com/en/emobility/products/editions/pv-edition
+[migrated 2026-08-18] Seed MID Status was 'No'; migrated to 'External' because notes describe a separate external MID meter ('MID meter (works with an external'). Original seed source: zeres.nl/laadpaal-check MID-me</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Integrated</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>KEBA P30 PV heeft een ingebouwde MID-gecertificeerde meter. Bevestigd via KEBA productinformatie. [read as Integrated: list says 'Ja' and the note does not qualify it]</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>cfl_0014</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>chg_0213</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Mennekes</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AMTRON 4You 310</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>MID Register</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>No MID meter | Solar/PV charging tier with RFID; page confirms use of an EXTERNAL energy meter for load management, no built-in MID meter.
+[migrated 2026-08-18] Seed MID Status was 'No'; migrated to 'Unknown' because seed value 'No' but the notes state 'No MID' — the evidence points both ways, so this is not established. Original seed source: Mennekes official (mennekes.org).</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Nee</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Geen MID meter. [read as None: list says 'Nee' and the note does not qualify it]</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>cfl_0015</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>chg_0245</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Raedian</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NEO</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>MID Register</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>No MID in base model | 'MID Certified Class B (+/-1% Accuracy)', EN 50470-3/EN 62053-23, 1000 imp/kWh pulse output. Single-phase up to 7.4kW, three-phase up to 22kW.
+[migrated 2026-08-18] Seed MID Status was 'Yes'; migrated to 'Unknown' because seed value 'Yes' but the notes state 'No MID' — the evidence points both ways, so this is not established. Original seed source: Raedian official (raedian.com).</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Nee</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Raedian NEO (basis) heeft geen MID-meter. Bevestigd in Raedian NEO datasheet Rev 2.1: 'No MID meter' bij het basis model. [read as None: list says 'Nee' and the note does not qualify it]</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>cfl_0016</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>chg_0246</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Raedian</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Neo 22 T7 5.S</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>MID Register</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>NEO variant with MID meter | CONSOLIDATED: this is not a distinct model -- it's a reseller/distributor SKU-configuration code (22kW, Type 2, ~5m cable, socket variant) for the base NEO product above. Merged; see NEO row for datasheet/MID status.
+[migrated 2026-08-18] Seed MID Status was 'Yes'; migrated to 'Optional' because notes describe a MID option or variant ('variant with MID'). Original seed source: Reseller Wallbox Discounter SKU code.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Integrated</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Dit is ook een NEO maar wel met MID meter. [read as Integrated: list says 'Ja' and the note does not qualify it]</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>cfl_0017</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>chg_0249</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Raedian</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NORA</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>MID Register</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Built-in MID meter | Portable/mobile AC wallbox, 7/11/22kW, CEE-plug or hardwired. Unlike NEO/NEX/Gemini, neither the product page nor the user manual explicitly mentions MID -- genuine gap, not just a fetch artifact. Raedian also sells DC fast chargers (Galaxy W 30/40kW, Galaxy V 50/60/80kW), not in seed data and not yet researched -- flag for a future pass.
+[migrated 2026-08-18] Seed MID Status was 'Maybe'; migrated to 'Optional' because seed value 'Maybe' mapped directly. Original seed source: Raedian official (raedian.com).</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Integrated</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Raedian Nora heeft een ingebouwde MID-gecertificeerde meter. Bevestigd via Raedian productinformatie. [read as Integrated: list says 'Ja' and the note does not qualify it]</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>cfl_0018</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>chg_0257</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ratio Electric</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Solid</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>MID Register</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Built-in MID meter | CORRECTION vs seed (was Yes): official spec table shows 'With MID compliant energy meter: No' across all 3 listed SKUs -- has a built-in kWh meter but it's NOT MID-certified/billing-grade.
+[migrated 2026-08-18] Seed MID Status was 'No'; migrated to 'None' because seed value 'No' mapped directly. Original seed source: Ratio Electric official (ratio-electric.com).</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Integrated</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Ratio Electric Solid heeft een ingebouwde MID-gecertificeerde meter. Bevestigd via Ratio Electric productinformatie. [read as Integrated: list says 'Ja' and the note does not qualify it]</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>cfl_0019</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>chg_0279</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>SMA</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>EV Charger 22</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>MID Register</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>MID meter but not billing suitable | Same physical legacy model/datasheet as 'EV Charger 7.4/22 (discontinued)' row above (power-rating variant, not a separate SKU) -- see that row for the current source.
+[migrated 2026-08-18] Seed MID Status was 'Yes'; migrated to 'Unknown' because seed value 'Yes' but the notes rule out the MID option they mention — seed and notes disagree, so this is not established. Original seed source: zeres.nl/laadpaal-check MID-meter list.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>SMA bevestigt op eigen website: 'SMA EV Charger is implemented with an MID-compliant energy meter, but is not suitable for billing purposes'. De 22kW variant heeft een MID-meter maar is niet geschikt voor werkgeverdeclaratie. [read as Optional: note describes an option or variant ('variant heeft een MID')]</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>cfl_0020</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>chg_0288</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Smappee</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>EV Wall</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>MID Register</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Built-in MID meter | MID Class B metering confirmed standard on all units (no non-MID SKU found). Direct /app/uploads/ links 404 frequently -- use the /eu/files/ redirector which always resolves to the latest revision.
+[migrated 2026-08-18] Seed MID Status was 'Yes'; migrated to 'Unknown' because seed value 'Yes' but the notes state 'non-MID' — the evidence points both ways, so this is not established. Original seed source: Smappee official (smappee.com), current model code EVWC/EVW4.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Integrated</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Smappee EV Wall heeft een ingebouwde MID-gecertificeerde energiemeter. [read as Integrated: list says 'Ja' and the note does not qualify it]</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>cfl_0021</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>chg_0341</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Volt time</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Source 1</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>MID Register</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Built-in MID meter | No search results, official page, reseller listing, or archive references a 'Source 1' model. Volt Time's base legacy model appears to simply be called 'Source' (per a firmware-files support article title). Recommend removing or renaming pending vendor confirmation.
+[migrated 2026-08-18] Seed MID Status was 'N/A'; migrated to 'Unknown' because seed value 'N/A' mapped directly. Original seed source: Extensive WebSearch -- no results.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Integrated</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Volt time Source 1 heeft een ingebouwde MID-gecertificeerde energiemeter. Bevestigd via Volt time productdatasheet. [read as Integrated: list says 'Ja' and the note does not qualify it]</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>cfl_0022</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>chg_0342</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Volt time</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Source 2</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>MID Register</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Built-in MID meter | Legacy model, not on current site navigation. 2023-dated brochure lists MID as an OPTIONAL upgrade ('Optioneel: MID 2014/32/EU gecertificeerd (&lt;1%)'), not standard/built-in.
+[migrated 2026-08-18] Seed MID Status was 'Maybe'; migrated to 'Optional' because notes describe a MID option or variant ('MID as an OPTIONAL'). Original seed source: Volt Time official archive (volttime.com, May 2023 brochure).</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Integrated</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Volt time Source 2 heeft een ingebouwde MID-gecertificeerde energiemeter. Bevestigd via Volt time productdatasheet. [read as Integrated: list says 'Ja' and the note does not qualify it]</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>cfl_0023</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>chg_0343</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Volt time</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Source 2s</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>MID Register</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Standard has no MID meter | Legacy model but still appears as a live SKU at portal.volttime.com/shop -- treat as still-sold legacy stock rather than fully discontinued.
+[migrated 2026-08-18] Seed MID Status was 'Unknown'; migrated to 'Unknown' because seed value 'Unknown' mapped directly. Original seed source: Distributor Alp-EV (Jan 2025 datasheet).</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Nee</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Volt time Source 2s (standaard) heeft geen ingebouwde MID-meter. Bevestigd via Volt time website. [read as None: list says 'Nee' and the note does not qualify it]</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>cfl_0024</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>chg_0340</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Volt time</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>One Pro</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>MID Register</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Built-in MID meter | No search results, official page, or reseller listing references a 'One Pro' charger. Possibly a seed-data conflation with 'Two Pro,' or an unreleased/renamed SKU. Recommend removing pending vendor confirmation.
+[migrated 2026-08-18] Seed MID Status was 'N/A'; migrated to 'Unknown' because seed value 'N/A' mapped directly. Original seed source: Extensive WebSearch -- no results.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Integrated</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Volt time One Pro heeft een ingebouwde MID-gecertificeerde energiemeter. Bevestigd via Volt time website. [read as Integrated: list says 'Ja' and the note does not qualify it]</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>cfl_0025</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>chg_0363</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Webasto</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Unite</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>MID Register</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Built-in MID meter | Confirmed distinct MID vs non-MID SKUs exist as separate part numbers (e.g. reseller part 5111685A has 'MID' literally in the SKU code). Official 'Documentation' page lists only 'Flyer' + 'EU Conformity Declarations' categories for Unite (no dedicated 'Datasheet' PDF found this round) — currently-filed Conrad-mirror datasheet remains the best available source. NOTE: in April 2024 Webasto sold majority stake in its EV Charging Systems business to Transom Capital (now trading as 'Ampure' globally) but the EU-facing charging.webasto.com site is still live and Webasto-branded</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Integrated</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Webasto Unite heeft een ingebouwde MID-gecertificeerde energiemeter. Bevestigd via Webasto productinformatie. [read as Integrated: list says 'Ja' and the note does not qualify it]</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>cfl_0026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>chg_0373</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Zaptec</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Go</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>MID Register</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Original has no standard MID; Go 2 has MID | Confirmed: 'Integrated energy meter, ~3% accuracy on readings' — not billing-grade. Still listed as current alongside Go 2 (simpler/base home unit).
+[migrated 2026-08-18] Seed MID Status was 'No'; migrated to 'None' because seed value 'No' mapped directly. Original seed source: Zaptec official (help.zaptec.com, content-verified).</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Nee</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Zaptec Go (origineel model) heeft geen standaard ingebouwde MID-meter; MID was een tijdelijk beschikbare optie. Opvolger Zaptec Go 2 heeft wel standaard MID. [read as Optional: note describes an option or variant ('MID was een tijdelijk beschikbare optie')]</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>cfl_0027</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>chg_0375</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Zaptec</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Pro</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>MID Register</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Zeres laadpalen list v19 Aug 2026</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Built-in MID meter | CORRECTION vs. Zeres seed data (was 'Yes'): the BASE 'Pro' SKU has NO built-in MID meter — MID is a separate SKU 'Zaptec Pro MID' (see new row below). 22kW/32A three-phase, 7.4kW single-phase.
+[migrated 2026-08-18] Seed MID Status was 'No'; migrated to 'Unknown' because seed value 'No' but the notes state 'NO built-in MID' — the evidence points both ways, so this is not established. Original seed source: zeres.nl/laadpaal-check MID-meter list.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Integrated</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Zaptec Pro heeft een ingebouwde MID-gecertificeerde energiemeter. Bevestigd via Zaptec Help Center en evplug.eu. [read as Integrated: list says 'Ja' and the note does not qualify it]</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -34795,7 +40849,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G385"/>
+  <dimension ref="A1:G479"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -49049,6 +55103,3108 @@
       <c r="G385" t="inlineStr">
         <is>
           <t>notes describe a MID option or variant ('MID-certified (ALE3D5FD10C3A00) version')</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>cfl_0001</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>conflict</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr"/>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>opened: MID Register says Integrated, Zeres laadpalen list v19 Aug 2026 says Ja (Optional)</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026. note describes an option or variant ('MID-gecertificeerde meter in de + variant')</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>cfl_0002</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>conflict</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr"/>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>opened: MID Register says Integrated, Zeres laadpalen list v19 Aug 2026 says Ja (Optional)</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026. note describes an option or variant ('MID-gecertificeerde meter in de + variant')</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>cfl_0003</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>conflict</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr"/>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>opened: MID Register says Unknown, Zeres laadpalen list v19 Aug 2026 says Nee (None)</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026. list says 'Nee' and the note does not qualify it</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>cfl_0004</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>conflict</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr"/>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>opened: MID Register says Optional, Zeres laadpalen list v19 Aug 2026 says Nee (None)</t>
+        </is>
+      </c>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026. list says 'Nee' and the note does not qualify it</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>cfl_0005</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>conflict</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr"/>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>opened: MID Register says Optional, Zeres laadpalen list v19 Aug 2026 says Ja (Integrated)</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026. list says 'Ja' and the note does not qualify it</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>cfl_0006</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>conflict</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr"/>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>opened: MID Register says Optional, Zeres laadpalen list v19 Aug 2026 says Ja (Integrated)</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026. list says 'Ja' and the note does not qualify it</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>cfl_0007</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>conflict</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr"/>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>opened: MID Register says Unknown, Zeres laadpalen list v19 Aug 2026 says Nee (None)</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026. list says 'Nee' and the note does not qualify it</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>cfl_0008</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>conflict</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr"/>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>opened: MID Register says Unknown, Zeres laadpalen list v19 Aug 2026 says Nee (None)</t>
+        </is>
+      </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026. list says 'Nee' and the note does not qualify it</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>cfl_0009</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>conflict</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr"/>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>opened: MID Register says Unknown, Zeres laadpalen list v19 Aug 2026 says Nee (None)</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026. list says 'Nee' and the note does not qualify it</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>cfl_0010</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>conflict</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr"/>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>opened: MID Register says Optional, Zeres laadpalen list v19 Aug 2026 says Ja (Integrated)</t>
+        </is>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026. list says 'Ja' and the note does not qualify it</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>cfl_0011</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>conflict</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr"/>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>opened: MID Register says Unknown, Zeres laadpalen list v19 Aug 2026 says Nee (None)</t>
+        </is>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026. list says 'Nee' and the note does not qualify it</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>cfl_0012</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>conflict</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr"/>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>opened: MID Register says Unknown, Zeres laadpalen list v19 Aug 2026 says Nee (None)</t>
+        </is>
+      </c>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026. list says 'Nee' and the note does not qualify it</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>cfl_0013</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>conflict</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr"/>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>opened: MID Register says External, Zeres laadpalen list v19 Aug 2026 says Ja (Integrated)</t>
+        </is>
+      </c>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026. list says 'Ja' and the note does not qualify it</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>cfl_0014</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>conflict</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr"/>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>opened: MID Register says Unknown, Zeres laadpalen list v19 Aug 2026 says Nee (None)</t>
+        </is>
+      </c>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026. list says 'Nee' and the note does not qualify it</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>cfl_0015</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>conflict</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr"/>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>opened: MID Register says Unknown, Zeres laadpalen list v19 Aug 2026 says Nee (None)</t>
+        </is>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026. list says 'Nee' and the note does not qualify it</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>cfl_0016</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>conflict</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr"/>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>opened: MID Register says Optional, Zeres laadpalen list v19 Aug 2026 says Ja (Integrated)</t>
+        </is>
+      </c>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026. list says 'Ja' and the note does not qualify it</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>cfl_0017</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>conflict</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr"/>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>opened: MID Register says Optional, Zeres laadpalen list v19 Aug 2026 says Ja (Integrated)</t>
+        </is>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026. list says 'Ja' and the note does not qualify it</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>cfl_0018</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>conflict</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr"/>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>opened: MID Register says None, Zeres laadpalen list v19 Aug 2026 says Ja (Integrated)</t>
+        </is>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026. list says 'Ja' and the note does not qualify it</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>cfl_0019</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>conflict</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr"/>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>opened: MID Register says Unknown, Zeres laadpalen list v19 Aug 2026 says Ja (Optional)</t>
+        </is>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026. note describes an option or variant ('variant heeft een MID')</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>cfl_0020</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>conflict</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr"/>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>opened: MID Register says Unknown, Zeres laadpalen list v19 Aug 2026 says Ja (Integrated)</t>
+        </is>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026. list says 'Ja' and the note does not qualify it</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>cfl_0021</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>conflict</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr"/>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>opened: MID Register says Unknown, Zeres laadpalen list v19 Aug 2026 says Ja (Integrated)</t>
+        </is>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026. list says 'Ja' and the note does not qualify it</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>cfl_0022</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>conflict</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr"/>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>opened: MID Register says Optional, Zeres laadpalen list v19 Aug 2026 says Ja (Integrated)</t>
+        </is>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026. list says 'Ja' and the note does not qualify it</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>cfl_0023</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>conflict</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr"/>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>opened: MID Register says Unknown, Zeres laadpalen list v19 Aug 2026 says Nee (None)</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026. list says 'Nee' and the note does not qualify it</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>cfl_0024</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>conflict</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr"/>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>opened: MID Register says Unknown, Zeres laadpalen list v19 Aug 2026 says Ja (Integrated)</t>
+        </is>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026. list says 'Ja' and the note does not qualify it</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>cfl_0025</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>conflict</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr"/>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>opened: MID Register says Unknown, Zeres laadpalen list v19 Aug 2026 says Ja (Integrated)</t>
+        </is>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026. list says 'Ja' and the note does not qualify it</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>cfl_0026</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>conflict</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr"/>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>opened: MID Register says None, Zeres laadpalen list v19 Aug 2026 says Nee (Optional)</t>
+        </is>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026. note describes an option or variant ('MID was een tijdelijk beschikbare optie')</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>cfl_0027</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>conflict</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr"/>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>opened: MID Register says Unknown, Zeres laadpalen list v19 Aug 2026 says Ja (Integrated)</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026. list says 'Ja' and the note does not qualify it</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>chg_0381</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr"/>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>created AlphaESS SMILE G3 ECVT</t>
+        </is>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026: listed 'Nee'. list says 'Nee' and the note does not qualify it</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>chg_0382</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr"/>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>created Autel Ultra</t>
+        </is>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026: listed 'Nee'. the note says this is not on the EU market ('Noord-Amerikaanse markt'); a charger that cannot be bought here cannot be booked into the REV, whatever its metering</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>chg_0383</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr"/>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>created Autel Wallbox AC MaxiCharger</t>
+        </is>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026: listed 'Ja'. list says 'Ja' and the note does not qualify it</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>chg_0384</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr"/>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>created Autel Pro</t>
+        </is>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026: listed 'Nee'. the note says this is not on the EU market ('Noord-Amerikaanse markt'); a charger that cannot be bought here cannot be booked into the REV, whatever its metering</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>chg_0385</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr"/>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>created Besen BS20 (alle varianten)</t>
+        </is>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026: listed 'Nee'. list says 'Nee' and the note does not qualify it</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>chg_0386</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr"/>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>created BlueBuilt (Coolblue) Prodrive (met M23/M24 op de laadpaal)</t>
+        </is>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026: listed 'Ja'. list says 'Ja' and the note does not qualify it</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>chg_0387</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr"/>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>created Blue Current Hidden</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026: listed 'Ja'. list says 'Ja' and the note does not qualify it</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>chg_0388</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr"/>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>created Bue Marble Ostra Home of Home &amp; Work</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026: listed 'Misschien'. list says 'Misschien' and the note does not qualify it</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>chg_0389</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr"/>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>created Cfos Brain Power wallbox 22kW Gen 1</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026: listed 'Ja'. list says 'Ja' and the note does not qualify it</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>chg_0390</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr"/>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>created CoolBlue BlueBuilt 1 model</t>
+        </is>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026: listed 'Misschien'. note describes an option or variant ('MID-meter is een optie')</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>chg_0391</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr"/>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>created Cube Basic</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026: listed 'Misschien'. list says 'Misschien' and the note does not qualify it</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>chg_0392</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr"/>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>created Cube Smart+</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026: listed 'Misschien'. list says 'Misschien' and the note does not qualify it</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>chg_0393</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr"/>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>created DIC Charge Easy</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026: listed 'Ja'. list says 'Ja' and the note does not qualify it</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>chg_0394</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr"/>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>created DIC Laadzuil</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026: listed 'Ja'. list says 'Ja' and the note does not qualify it</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>chg_0395</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr"/>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>created Easee Up</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026: listed 'Nee'. list says 'Nee' and the note does not qualify it</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>chg_0396</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr"/>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>created Easee Max</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026: listed 'Ja'. list says 'Ja' and the note does not qualify it</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>chg_0397</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr"/>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>created Easee Core</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026: listed 'Nee'. list says 'Nee' and the note does not qualify it</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>chg_0398</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr"/>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>created Ecotap Duo Wide XL</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026: listed 'Ja'. list says 'Ja' and the note does not qualify it</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>chg_0399</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr"/>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>created Ecotap Duo Wide Plus</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026: listed 'Ja'. list says 'Ja' and the note does not qualify it</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>chg_0400</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr"/>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>created Elli Connect 2</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026: listed 'Nee'. list says 'Nee' and the note does not qualify it</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>chg_0401</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr"/>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>created Elli Charger Pro (2)</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026: listed 'Ja'. list says 'Ja' and the note does not qualify it</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>chg_0402</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr"/>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>created Eneco Mobility Connectric</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026: listed 'Ja'. list says 'Ja' and the note does not qualify it</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>chg_0403</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr"/>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>created Flexicharge Home</t>
+        </is>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026: listed 'Ja'. list says 'Ja' and the note does not qualify it</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>chg_0404</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr"/>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>created Flexicharge Business Duo/Business Solo</t>
+        </is>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026: listed 'Ja'. list says 'Ja' and the note does not qualify it</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>chg_0405</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr"/>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>created Flexicharge Business Wall Duo/Business Wall Solo</t>
+        </is>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026: listed 'Ja'. list says 'Ja' and the note does not qualify it</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>chg_0406</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr"/>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>created Flexicharge Business Transport</t>
+        </is>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026: listed 'Ja'. list says 'Ja' and the note does not qualify it</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>chg_0407</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr"/>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>created Flexicharge Public</t>
+        </is>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026: listed 'Ja'. list says 'Ja' and the note does not qualify it</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>chg_0408</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr"/>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>created Garo GLB (Entity, GLB, Wallbox)</t>
+        </is>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026: listed 'Nee'. list says 'Nee' and the note does not qualify it</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>chg_0409</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr"/>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>created go-e Flex of Core</t>
+        </is>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026: listed 'Nee'. list says 'Nee' and the note does not qualify it</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>chg_0410</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr"/>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>created go-e Charger Pro</t>
+        </is>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026: listed 'Ja'. list says 'Ja' and the note does not qualify it</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>chg_0411</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr"/>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>created Hey One Connect Plus en de One Smart</t>
+        </is>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026: listed 'Ja'. list says 'Ja' and the note does not qualify it</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>chg_0412</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr"/>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>created Inepro Pro380 MID</t>
+        </is>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026: listed 'Ja'. list says 'Ja' and the note does not qualify it</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>chg_0413</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr"/>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>created KEBA P30 A-series</t>
+        </is>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026: listed 'Nee'. list says 'Nee' and the note does not qualify it</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>chg_0414</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr"/>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>created KEBA P30 C-series</t>
+        </is>
+      </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026: listed 'Misschien'. note describes an option or variant ('als optie')</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>chg_0415</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr"/>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>created KEBA P30 X-series</t>
+        </is>
+      </c>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026: listed 'Misschien'. note describes an option or variant ('als optie')</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>chg_0416</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr"/>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>created Loxone Wallbox 11kW 16A Tree (MID-variant)</t>
+        </is>
+      </c>
+      <c r="G448" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026: listed 'Misschien'. note describes an option or variant ('als Optie')</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>chg_0417</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr"/>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>created Mennekes Amtron  4you 640</t>
+        </is>
+      </c>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026: listed 'Ja'. list says 'Ja' and the note does not qualify it</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>chg_0418</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr"/>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>created NexBlue Edge Max  en Delta Max</t>
+        </is>
+      </c>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026: listed 'Ja'. list says 'Ja' and the note does not qualify it</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>chg_0419</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr"/>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>created Ohme Home  of Pod</t>
+        </is>
+      </c>
+      <c r="G451" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026: listed 'Nee'. list says 'Nee' and the note does not qualify it</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>chg_0420</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr"/>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>created Ohme Home Pro</t>
+        </is>
+      </c>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026: listed 'Nee'. list says 'Nee' and the note does not qualify it</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>chg_0421</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr"/>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>created Ratio Electric IO6</t>
+        </is>
+      </c>
+      <c r="G453" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026: listed 'Nee'. list says 'Nee' and the note does not qualify it</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>chg_0422</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr"/>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>created Ratio Electric IO7 Double MID</t>
+        </is>
+      </c>
+      <c r="G454" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026: listed 'Ja'. list says 'Ja' and the note does not qualify it</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>chg_0423</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr"/>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>created Schneider Charge Pro</t>
+        </is>
+      </c>
+      <c r="G455" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026: listed 'Ja'. list says 'Ja' and the note does not qualify it</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>chg_0424</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr"/>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>created Shell Recharge (NewMotion) Home Advanced 1.0 of 1.1</t>
+        </is>
+      </c>
+      <c r="G456" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026: listed 'Nee'. list says 'Nee' and the note does not qualify it</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>chg_0425</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr"/>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>created Sigenergy Sigen EV AC</t>
+        </is>
+      </c>
+      <c r="G457" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026: listed 'Nee'. list says 'Nee' and the note does not qualify it</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>chg_0426</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr"/>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>created SMA EV Charger 7.4</t>
+        </is>
+      </c>
+      <c r="G458" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026: listed 'Ja'. note describes an option or variant ('variant heeft een MID')</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>chg_0427</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr"/>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>created Smappee EV Dual</t>
+        </is>
+      </c>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026: listed 'Ja'. list says 'Ja' and the note does not qualify it</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>chg_0428</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr"/>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>created Smappe UV Ultra</t>
+        </is>
+      </c>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026: listed 'Nee'. list says 'Nee' and the note does not qualify it</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>chg_0429</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr"/>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>created SolarEdge EV Charger (oud model)</t>
+        </is>
+      </c>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026: listed 'Misschien'. note describes an option or variant ('als optie')</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>chg_0430</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr"/>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>created SolarEdge ONE EV Charger Pro (SE-EVN22P)</t>
+        </is>
+      </c>
+      <c r="G462" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026: listed 'Ja'. list says 'Ja' and the note does not qualify it</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>chg_0431</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr"/>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>created SolarLife 1 model bekend</t>
+        </is>
+      </c>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026: listed 'Ja'. list says 'Ja' and the note does not qualify it</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>chg_0432</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr"/>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>created Spelsberg Wallbox</t>
+        </is>
+      </c>
+      <c r="G464" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026: listed 'Ja'. list says 'Ja' and the note does not qualify it</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>chg_0433</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr"/>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>created Sunpower Drive AC Charger</t>
+        </is>
+      </c>
+      <c r="G465" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026: listed 'Nee'. list says 'Nee' and the note does not qualify it</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>chg_0434</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr"/>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>created Tesla Wall Connector Generation 1</t>
+        </is>
+      </c>
+      <c r="G466" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026: listed 'Nee'. note describes an option or variant ('MID was een tijdelijk beschikbare optie')</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>chg_0435</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr"/>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>created Tesla Wall Connector Generation 2</t>
+        </is>
+      </c>
+      <c r="G467" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026: listed 'Nee'. note describes an option or variant ('MID was een tijdelijk beschikbare optie')</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>chg_0436</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr"/>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>created Tesla Wall Connector Generation 3</t>
+        </is>
+      </c>
+      <c r="G468" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026: listed 'Nee'. list says 'Nee' and the note does not qualify it</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>chg_0437</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr"/>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>created Tesla Wall Connector Generation 3 MID</t>
+        </is>
+      </c>
+      <c r="G469" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026: listed 'Ja'. list says 'Ja' and the note does not qualify it</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>chg_0438</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr"/>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>created Tinkerforge WARP3</t>
+        </is>
+      </c>
+      <c r="G470" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026: listed 'Ja'. list says 'Ja' and the note does not qualify it</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>chg_0439</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr"/>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>created van Mossel Energie 11, 22 kW OneCharge</t>
+        </is>
+      </c>
+      <c r="G471" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026: listed 'Ja'. list says 'Ja' and the note does not qualify it</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>chg_0440</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr"/>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>created Vestel (Amazon) Wallbox EVC04-AC11-11 kW</t>
+        </is>
+      </c>
+      <c r="G472" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026: listed 'Nee'. note describes an option or variant ('MID was optie')</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>chg_0441</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr"/>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>created Volkswagen ID. Charger Pro</t>
+        </is>
+      </c>
+      <c r="G473" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026: listed 'Ja'. list says 'Ja' and the note does not qualify it</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>chg_0442</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr"/>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>created Voldt Mobile OCPP Charger</t>
+        </is>
+      </c>
+      <c r="G474" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026: listed 'Ja'. list says 'Ja' and the note does not qualify it</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>chg_0443</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr"/>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>created Volvo Wallbox GHO22E21</t>
+        </is>
+      </c>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026: listed 'Ja'. list says 'Ja' and the note does not qualify it</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>chg_0444</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr"/>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>created Wallbox Pulsar Pro MID</t>
+        </is>
+      </c>
+      <c r="G476" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026: listed 'Ja'. list says 'Ja' and the note does not qualify it</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>chg_0445</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr"/>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>created WissEnergy Alle typen</t>
+        </is>
+      </c>
+      <c r="G477" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026: listed 'Nee'. note describes an option or variant ('MID is optie')</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>chg_0446</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr"/>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>created Zappi (Myenergi) 2.1</t>
+        </is>
+      </c>
+      <c r="G478" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026: listed 'Nee'. list says 'Nee' and the note does not qualify it</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>2026-08-20 18:48:25</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>root</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>chg_0447</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr"/>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>created Zonneplan Charge en Charge 2</t>
+        </is>
+      </c>
+      <c r="G479" t="inlineStr">
+        <is>
+          <t>Imported from Zeres laadpalen list v19 Aug 2026: listed 'Nee'. list says 'Nee' and the note does not qualify it</t>
         </is>
       </c>
     </row>

--- a/data/Zeres_MID_Register.xlsx
+++ b/data/Zeres_MID_Register.xlsx
@@ -27546,11 +27546,7 @@
       </c>
       <c r="G387" t="inlineStr"/>
       <c r="H387" t="inlineStr"/>
-      <c r="I387" t="inlineStr">
-        <is>
-          <t>M23 of M24 op laadpaal zichtbaar</t>
-        </is>
-      </c>
+      <c r="I387" t="inlineStr"/>
       <c r="J387" t="inlineStr"/>
       <c r="K387" t="inlineStr">
         <is>
@@ -27578,7 +27574,8 @@
       <c r="R387" t="inlineStr">
         <is>
           <t>Aanvankelijk heeft Coolblue laders zonder MID meter geleverd met deze naam. Met Prodrive zijn de laadpalen wel voorzien van een MID meter
-[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Ja'; recorded as Integrated because list says 'Ja' and the note does not qualify it.</t>
+[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Ja'; recorded as Integrated because list says 'Ja' and the note does not qualify it.
+Source column (not a URL): M23 of M24 op laadpaal zichtbaar</t>
         </is>
       </c>
       <c r="S387" t="inlineStr"/>
@@ -27612,11 +27609,7 @@
       </c>
       <c r="G388" t="inlineStr"/>
       <c r="H388" t="inlineStr"/>
-      <c r="I388" t="inlineStr">
-        <is>
-          <t>Datasheet ontvangen van Blue Current</t>
-        </is>
-      </c>
+      <c r="I388" t="inlineStr"/>
       <c r="J388" t="inlineStr"/>
       <c r="K388" t="inlineStr">
         <is>
@@ -27644,7 +27637,8 @@
       <c r="R388" t="inlineStr">
         <is>
           <t>Blue Current Hidden heeft een MID-meter . Bevestigd via Blue Current productsheet.
-[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Ja'; recorded as Integrated because list says 'Ja' and the note does not qualify it.</t>
+[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Ja'; recorded as Integrated because list says 'Ja' and the note does not qualify it.
+Source column (not a URL): Datasheet ontvangen van Blue Current</t>
         </is>
       </c>
       <c r="S388" t="inlineStr"/>
@@ -28004,11 +27998,7 @@
       </c>
       <c r="G394" t="inlineStr"/>
       <c r="H394" t="inlineStr"/>
-      <c r="I394" t="inlineStr">
-        <is>
-          <t>Bevestigd door fabrikant: document beschikbaar bij Zeres</t>
-        </is>
-      </c>
+      <c r="I394" t="inlineStr"/>
       <c r="J394" t="inlineStr"/>
       <c r="K394" t="inlineStr">
         <is>
@@ -28036,7 +28026,8 @@
       <c r="R394" t="inlineStr">
         <is>
           <t>DIC Charge Easy, model 50122 heeft een MID meter
-[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Ja'; recorded as Integrated because list says 'Ja' and the note does not qualify it.</t>
+[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Ja'; recorded as Integrated because list says 'Ja' and the note does not qualify it.
+Source column (not a URL): Bevestigd door fabrikant: document beschikbaar bij Zeres</t>
         </is>
       </c>
       <c r="S394" t="inlineStr"/>
@@ -28070,11 +28061,7 @@
       </c>
       <c r="G395" t="inlineStr"/>
       <c r="H395" t="inlineStr"/>
-      <c r="I395" t="inlineStr">
-        <is>
-          <t>Bevestigd door fabrikant: document beschikbaar bij Zeres</t>
-        </is>
-      </c>
+      <c r="I395" t="inlineStr"/>
       <c r="J395" t="inlineStr"/>
       <c r="K395" t="inlineStr">
         <is>
@@ -28102,7 +28089,8 @@
       <c r="R395" t="inlineStr">
         <is>
           <t>DIC Laadzuil: heeft wel MID meter.
-[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Ja'; recorded as Integrated because list says 'Ja' and the note does not qualify it.</t>
+[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Ja'; recorded as Integrated because list says 'Ja' and the note does not qualify it.
+Source column (not a URL): Bevestigd door fabrikant: document beschikbaar bij Zeres</t>
         </is>
       </c>
       <c r="S395" t="inlineStr"/>
@@ -28466,11 +28454,7 @@
       </c>
       <c r="G401" t="inlineStr"/>
       <c r="H401" t="inlineStr"/>
-      <c r="I401" t="inlineStr">
-        <is>
-          <t>Datasheet in verzameling Zeres</t>
-        </is>
-      </c>
+      <c r="I401" t="inlineStr"/>
       <c r="J401" t="inlineStr"/>
       <c r="K401" t="inlineStr">
         <is>
@@ -28498,7 +28482,8 @@
       <c r="R401" t="inlineStr">
         <is>
           <t>Voor Volkswagen, SKoda, Seat: geen MID meter.
-[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Nee'; recorded as None because list says 'Nee' and the note does not qualify it.</t>
+[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Nee'; recorded as None because list says 'Nee' and the note does not qualify it.
+Source column (not a URL): Datasheet in verzameling Zeres</t>
         </is>
       </c>
       <c r="S401" t="inlineStr"/>
@@ -28532,11 +28517,7 @@
       </c>
       <c r="G402" t="inlineStr"/>
       <c r="H402" t="inlineStr"/>
-      <c r="I402" t="inlineStr">
-        <is>
-          <t>Datasheet in verzameling Zeres</t>
-        </is>
-      </c>
+      <c r="I402" t="inlineStr"/>
       <c r="J402" t="inlineStr"/>
       <c r="K402" t="inlineStr">
         <is>
@@ -28564,7 +28545,8 @@
       <c r="R402" t="inlineStr">
         <is>
           <t>Voor Volkswagen, SKoda, Seat: wel MID meter.
-[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Ja'; recorded as Integrated because list says 'Ja' and the note does not qualify it.</t>
+[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Ja'; recorded as Integrated because list says 'Ja' and the note does not qualify it.
+Source column (not a URL): Datasheet in verzameling Zeres</t>
         </is>
       </c>
       <c r="S402" t="inlineStr"/>
@@ -28665,11 +28647,7 @@
       </c>
       <c r="G404" t="inlineStr"/>
       <c r="H404" t="inlineStr"/>
-      <c r="I404" t="inlineStr">
-        <is>
-          <t>opgave via website fabrikant</t>
-        </is>
-      </c>
+      <c r="I404" t="inlineStr"/>
       <c r="J404" t="inlineStr"/>
       <c r="K404" t="inlineStr">
         <is>
@@ -28697,7 +28675,8 @@
       <c r="R404" t="inlineStr">
         <is>
           <t>Al onze laadpalen worden standaard geleverd met een geïntegreerde MID‑gecertificeerde kWh‑meter
-[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Ja'; recorded as Integrated because list says 'Ja' and the note does not qualify it.</t>
+[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Ja'; recorded as Integrated because list says 'Ja' and the note does not qualify it.
+Source column (not a URL): opgave via website fabrikant</t>
         </is>
       </c>
       <c r="S404" t="inlineStr"/>
@@ -28731,11 +28710,7 @@
       </c>
       <c r="G405" t="inlineStr"/>
       <c r="H405" t="inlineStr"/>
-      <c r="I405" t="inlineStr">
-        <is>
-          <t>opgave via website fabrikant</t>
-        </is>
-      </c>
+      <c r="I405" t="inlineStr"/>
       <c r="J405" t="inlineStr"/>
       <c r="K405" t="inlineStr">
         <is>
@@ -28763,7 +28738,8 @@
       <c r="R405" t="inlineStr">
         <is>
           <t>Al onze laadpalen worden standaard geleverd met een geïntegreerde MID‑gecertificeerde kWh‑meter
-[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Ja'; recorded as Integrated because list says 'Ja' and the note does not qualify it.</t>
+[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Ja'; recorded as Integrated because list says 'Ja' and the note does not qualify it.
+Source column (not a URL): opgave via website fabrikant</t>
         </is>
       </c>
       <c r="S405" t="inlineStr"/>
@@ -28797,11 +28773,7 @@
       </c>
       <c r="G406" t="inlineStr"/>
       <c r="H406" t="inlineStr"/>
-      <c r="I406" t="inlineStr">
-        <is>
-          <t>opgave via website fabrikant</t>
-        </is>
-      </c>
+      <c r="I406" t="inlineStr"/>
       <c r="J406" t="inlineStr"/>
       <c r="K406" t="inlineStr">
         <is>
@@ -28829,7 +28801,8 @@
       <c r="R406" t="inlineStr">
         <is>
           <t>Al onze laadpalen worden standaard geleverd met een geïntegreerde MID‑gecertificeerde kWh‑meter
-[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Ja'; recorded as Integrated because list says 'Ja' and the note does not qualify it.</t>
+[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Ja'; recorded as Integrated because list says 'Ja' and the note does not qualify it.
+Source column (not a URL): opgave via website fabrikant</t>
         </is>
       </c>
       <c r="S406" t="inlineStr"/>
@@ -28863,11 +28836,7 @@
       </c>
       <c r="G407" t="inlineStr"/>
       <c r="H407" t="inlineStr"/>
-      <c r="I407" t="inlineStr">
-        <is>
-          <t>opgave via website fabrikant</t>
-        </is>
-      </c>
+      <c r="I407" t="inlineStr"/>
       <c r="J407" t="inlineStr"/>
       <c r="K407" t="inlineStr">
         <is>
@@ -28895,7 +28864,8 @@
       <c r="R407" t="inlineStr">
         <is>
           <t>Al onze laadpalen worden standaard geleverd met een geïntegreerde MID‑gecertificeerde kWh‑meter
-[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Ja'; recorded as Integrated because list says 'Ja' and the note does not qualify it.</t>
+[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Ja'; recorded as Integrated because list says 'Ja' and the note does not qualify it.
+Source column (not a URL): opgave via website fabrikant</t>
         </is>
       </c>
       <c r="S407" t="inlineStr"/>
@@ -28929,11 +28899,7 @@
       </c>
       <c r="G408" t="inlineStr"/>
       <c r="H408" t="inlineStr"/>
-      <c r="I408" t="inlineStr">
-        <is>
-          <t>opgave via website fabrikant</t>
-        </is>
-      </c>
+      <c r="I408" t="inlineStr"/>
       <c r="J408" t="inlineStr"/>
       <c r="K408" t="inlineStr">
         <is>
@@ -28961,7 +28927,8 @@
       <c r="R408" t="inlineStr">
         <is>
           <t>Al onze laadpalen worden standaard geleverd met een geïntegreerde MID‑gecertificeerde kWh‑meter
-[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Ja'; recorded as Integrated because list says 'Ja' and the note does not qualify it.</t>
+[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Ja'; recorded as Integrated because list says 'Ja' and the note does not qualify it.
+Source column (not a URL): opgave via website fabrikant</t>
         </is>
       </c>
       <c r="S408" t="inlineStr"/>
@@ -28995,11 +28962,7 @@
       </c>
       <c r="G409" t="inlineStr"/>
       <c r="H409" t="inlineStr"/>
-      <c r="I409" t="inlineStr">
-        <is>
-          <t>garo.se</t>
-        </is>
-      </c>
+      <c r="I409" t="inlineStr"/>
       <c r="J409" t="inlineStr"/>
       <c r="K409" t="inlineStr">
         <is>
@@ -29027,7 +28990,8 @@
       <c r="R409" t="inlineStr">
         <is>
           <t>Diverse modellen, wel met meter maar geen MID meter.
-[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Nee'; recorded as None because list says 'Nee' and the note does not qualify it.</t>
+[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Nee'; recorded as None because list says 'Nee' and the note does not qualify it.
+Source column (not a URL): garo.se</t>
         </is>
       </c>
       <c r="S409" t="inlineStr"/>
@@ -29193,11 +29157,7 @@
       </c>
       <c r="G412" t="inlineStr"/>
       <c r="H412" t="inlineStr"/>
-      <c r="I412" t="inlineStr">
-        <is>
-          <t>Bevestigd per email met productsheets door fabrikant.</t>
-        </is>
-      </c>
+      <c r="I412" t="inlineStr"/>
       <c r="J412" t="inlineStr"/>
       <c r="K412" t="inlineStr">
         <is>
@@ -29225,7 +29185,8 @@
       <c r="R412" t="inlineStr">
         <is>
           <t>Geschikt voor ERE: hebben een MID meter.
-[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Ja'; recorded as Integrated because list says 'Ja' and the note does not qualify it.</t>
+[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Ja'; recorded as Integrated because list says 'Ja' and the note does not qualify it.
+Source column (not a URL): Bevestigd per email met productsheets door fabrikant.</t>
         </is>
       </c>
       <c r="S412" t="inlineStr"/>
@@ -29977,11 +29938,7 @@
       </c>
       <c r="G424" t="inlineStr"/>
       <c r="H424" t="inlineStr"/>
-      <c r="I424" t="inlineStr">
-        <is>
-          <t>Zie Zeres datasheets</t>
-        </is>
-      </c>
+      <c r="I424" t="inlineStr"/>
       <c r="J424" t="inlineStr"/>
       <c r="K424" t="inlineStr">
         <is>
@@ -30009,7 +29966,8 @@
       <c r="R424" t="inlineStr">
         <is>
           <t>Heeft MID meter
-[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Ja'; recorded as Integrated because list says 'Ja' and the note does not qualify it.</t>
+[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Ja'; recorded as Integrated because list says 'Ja' and the note does not qualify it.
+Source column (not a URL): Zie Zeres datasheets</t>
         </is>
       </c>
       <c r="S424" t="inlineStr"/>
@@ -30303,11 +30261,7 @@
       </c>
       <c r="G429" t="inlineStr"/>
       <c r="H429" t="inlineStr"/>
-      <c r="I429" t="inlineStr">
-        <is>
-          <t>Zie Zeres docs</t>
-        </is>
-      </c>
+      <c r="I429" t="inlineStr"/>
       <c r="J429" t="inlineStr"/>
       <c r="K429" t="inlineStr">
         <is>
@@ -30335,7 +30289,8 @@
       <c r="R429" t="inlineStr">
         <is>
           <t>Geen MID meter
-[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Nee'; recorded as None because list says 'Nee' and the note does not qualify it.</t>
+[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Nee'; recorded as None because list says 'Nee' and the note does not qualify it.
+Source column (not a URL): Zie Zeres docs</t>
         </is>
       </c>
       <c r="S429" t="inlineStr"/>
@@ -30897,11 +30852,7 @@
       </c>
       <c r="G438" t="inlineStr"/>
       <c r="H438" t="inlineStr"/>
-      <c r="I438" t="inlineStr">
-        <is>
-          <t>Wall Connector Generation 3</t>
-        </is>
-      </c>
+      <c r="I438" t="inlineStr"/>
       <c r="J438" t="inlineStr"/>
       <c r="K438" t="inlineStr">
         <is>
@@ -30929,7 +30880,8 @@
       <c r="R438" t="inlineStr">
         <is>
           <t>Deze Wallconnector heeft wel een MID meter
-[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Ja'; recorded as Integrated because list says 'Ja' and the note does not qualify it.</t>
+[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Ja'; recorded as Integrated because list says 'Ja' and the note does not qualify it.
+Source column (not a URL): Wall Connector Generation 3</t>
         </is>
       </c>
       <c r="S438" t="inlineStr"/>
@@ -31487,11 +31439,7 @@
       </c>
       <c r="G447" t="inlineStr"/>
       <c r="H447" t="inlineStr"/>
-      <c r="I447" t="inlineStr">
-        <is>
-          <t>Zappi-2.1-T-EU_Datasheet_NL.pdf</t>
-        </is>
-      </c>
+      <c r="I447" t="inlineStr"/>
       <c r="J447" t="inlineStr"/>
       <c r="K447" t="inlineStr">
         <is>
@@ -31519,7 +31467,8 @@
       <c r="R447" t="inlineStr">
         <is>
           <t>Geen MID meter
-[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Nee'; recorded as None because list says 'Nee' and the note does not qualify it.</t>
+[imported 2026-08-20 from Zeres laadpalen list v19 Aug 2026] Listed as 'Nee'; recorded as None because list says 'Nee' and the note does not qualify it.
+Source column (not a URL): Zappi-2.1-T-EU_Datasheet_NL.pdf</t>
         </is>
       </c>
       <c r="S447" t="inlineStr"/>
@@ -55109,7 +55058,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -55142,7 +55091,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -55175,7 +55124,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -55208,7 +55157,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -55241,7 +55190,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -55274,7 +55223,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -55307,7 +55256,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -55340,7 +55289,7 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -55373,7 +55322,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -55406,7 +55355,7 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -55439,7 +55388,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -55472,7 +55421,7 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -55505,7 +55454,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -55538,7 +55487,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -55571,7 +55520,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -55604,7 +55553,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -55637,7 +55586,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -55670,7 +55619,7 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -55703,7 +55652,7 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -55736,7 +55685,7 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -55769,7 +55718,7 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -55802,7 +55751,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -55835,7 +55784,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -55868,7 +55817,7 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -55901,7 +55850,7 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -55934,7 +55883,7 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -55967,7 +55916,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -56000,7 +55949,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -56033,7 +55982,7 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -56066,7 +56015,7 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -56099,7 +56048,7 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -56132,7 +56081,7 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -56165,7 +56114,7 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
@@ -56198,7 +56147,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -56231,7 +56180,7 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -56264,7 +56213,7 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
@@ -56297,7 +56246,7 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
@@ -56330,7 +56279,7 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
@@ -56363,7 +56312,7 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
@@ -56396,7 +56345,7 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -56429,7 +56378,7 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
@@ -56462,7 +56411,7 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
@@ -56495,7 +56444,7 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
@@ -56528,7 +56477,7 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
@@ -56561,7 +56510,7 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -56594,7 +56543,7 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -56627,7 +56576,7 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
@@ -56660,7 +56609,7 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
@@ -56693,7 +56642,7 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
@@ -56726,7 +56675,7 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
@@ -56759,7 +56708,7 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
@@ -56792,7 +56741,7 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
@@ -56825,7 +56774,7 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
@@ -56858,7 +56807,7 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
@@ -56891,7 +56840,7 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
@@ -56924,7 +56873,7 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
@@ -56957,7 +56906,7 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
@@ -56990,7 +56939,7 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
@@ -57023,7 +56972,7 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
@@ -57056,7 +57005,7 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
@@ -57089,7 +57038,7 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
@@ -57122,7 +57071,7 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
@@ -57155,7 +57104,7 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
@@ -57188,7 +57137,7 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
@@ -57221,7 +57170,7 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
@@ -57254,7 +57203,7 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
@@ -57287,7 +57236,7 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
@@ -57320,7 +57269,7 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
@@ -57353,7 +57302,7 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
@@ -57386,7 +57335,7 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
@@ -57419,7 +57368,7 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
@@ -57452,7 +57401,7 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
@@ -57485,7 +57434,7 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
@@ -57518,7 +57467,7 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
@@ -57551,7 +57500,7 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
@@ -57584,7 +57533,7 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
@@ -57617,7 +57566,7 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
@@ -57650,7 +57599,7 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
@@ -57683,7 +57632,7 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
@@ -57716,7 +57665,7 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
@@ -57749,7 +57698,7 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
@@ -57782,7 +57731,7 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
@@ -57815,7 +57764,7 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
@@ -57848,7 +57797,7 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
@@ -57881,7 +57830,7 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
@@ -57914,7 +57863,7 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
@@ -57947,7 +57896,7 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
@@ -57980,7 +57929,7 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
@@ -58013,7 +57962,7 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
@@ -58046,7 +57995,7 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
@@ -58079,7 +58028,7 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
@@ -58112,7 +58061,7 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
@@ -58145,7 +58094,7 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
@@ -58178,7 +58127,7 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>2026-08-20 18:48:25</t>
+          <t>2026-08-20 18:54:39</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
